--- a/17 18 20/Excel/4.Advanced Tools & Automation/4.LogicalFunctions/Logical_Functions.xlsx
+++ b/17 18 20/Excel/4.Advanced Tools & Automation/4.LogicalFunctions/Logical_Functions.xlsx
@@ -9,12 +9,16 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072"/>
   </bookViews>
   <sheets>
-    <sheet name="ComparisonOperator" sheetId="13" r:id="rId1"/>
-    <sheet name="ConditionalFunctions" sheetId="19" r:id="rId2"/>
+    <sheet name="ComparisonOperator (2)" sheetId="20" r:id="rId1"/>
+    <sheet name="ComparisonOperator" sheetId="13" r:id="rId2"/>
+    <sheet name="ConditionalFunctions" sheetId="19" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ComparisonOperator (2)'!$A$1:$Z$22</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -25,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="118">
   <si>
     <t>EmpID</t>
   </si>
@@ -343,6 +347,42 @@
   </si>
   <si>
     <t>=IF(OR(LogTest01,LogTest02),ValueIfTrue,ValueIfFalse)</t>
+  </si>
+  <si>
+    <t>=</t>
+  </si>
+  <si>
+    <t>&lt;&gt;</t>
+  </si>
+  <si>
+    <t>&lt;</t>
+  </si>
+  <si>
+    <t>&gt;</t>
+  </si>
+  <si>
+    <t>&lt;=</t>
+  </si>
+  <si>
+    <t>&gt;=</t>
+  </si>
+  <si>
+    <t>before Appraisal</t>
+  </si>
+  <si>
+    <t>after appraisal</t>
+  </si>
+  <si>
+    <t>Lisa Tayloor</t>
+  </si>
+  <si>
+    <t>Alex Martineez</t>
+  </si>
+  <si>
+    <t>if(logic,value_True,Value_False)</t>
+  </si>
+  <si>
+    <t>=IF(LOGItES,VALUE_TRUE,VALUE_IFfALSE)</t>
   </si>
 </sst>
 </file>
@@ -353,7 +393,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -393,6 +433,14 @@
     <font>
       <u/>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -454,7 +502,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -511,13 +559,19 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="24">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -545,6 +599,166 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -874,6 +1088,1494 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Z22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="6.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.77734375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="5.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="17" width="10.77734375" style="2" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="26.5546875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="27" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="37.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="2.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="4.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="3.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="8.88671875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="5">
+        <v>46000</v>
+      </c>
+      <c r="G2" s="5">
+        <v>50000</v>
+      </c>
+      <c r="H2" s="5">
+        <v>2000</v>
+      </c>
+      <c r="I2" s="5">
+        <v>2</v>
+      </c>
+      <c r="J2" s="6">
+        <v>44668</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="L2" s="3" t="b">
+        <f>B2=C2</f>
+        <v>0</v>
+      </c>
+      <c r="M2" s="3" t="b">
+        <f>B2&lt;&gt;C2</f>
+        <v>1</v>
+      </c>
+      <c r="N2" s="3" t="b">
+        <f>F2&lt;G2</f>
+        <v>1</v>
+      </c>
+      <c r="O2" s="3" t="b">
+        <f>F2&gt;G2</f>
+        <v>0</v>
+      </c>
+      <c r="P2" s="3" t="b">
+        <f>F2&lt;=G2</f>
+        <v>1</v>
+      </c>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3" t="str">
+        <f>IF(F2&lt;G2,"Got Hike","No Hike")</f>
+        <v>Got Hike</v>
+      </c>
+      <c r="S2" s="2" t="str">
+        <f>IF(F2&lt;51000,"Low",IF(F2&lt;68000,"Avg","High"))</f>
+        <v>Low</v>
+      </c>
+      <c r="T2" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="W2" s="22" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="5">
+        <v>45000</v>
+      </c>
+      <c r="G3" s="5">
+        <v>80000</v>
+      </c>
+      <c r="H3" s="5">
+        <v>2200</v>
+      </c>
+      <c r="I3" s="5">
+        <v>2</v>
+      </c>
+      <c r="J3" s="6">
+        <v>44448</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="L3" s="3" t="b">
+        <f t="shared" ref="L3:L21" si="0">B3=C3</f>
+        <v>1</v>
+      </c>
+      <c r="M3" s="3" t="b">
+        <f t="shared" ref="M3:M21" si="1">B3&lt;&gt;C3</f>
+        <v>0</v>
+      </c>
+      <c r="N3" s="3" t="b">
+        <f t="shared" ref="N3:N21" si="2">F3&lt;G3</f>
+        <v>1</v>
+      </c>
+      <c r="O3" s="3" t="b">
+        <f t="shared" ref="O3:O21" si="3">F3&gt;G3</f>
+        <v>0</v>
+      </c>
+      <c r="P3" s="3" t="b">
+        <f t="shared" ref="P3:P21" si="4">F3&lt;=G3</f>
+        <v>1</v>
+      </c>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3" t="str">
+        <f>IF(F3&lt;G3,"Got Hike","No Hike")</f>
+        <v>Got Hike</v>
+      </c>
+      <c r="S3" s="2" t="str">
+        <f t="shared" ref="S3:S21" si="5">IF(F3&lt;51000,"Low",IF(F3&lt;68000,"Avg","High"))</f>
+        <v>Low</v>
+      </c>
+      <c r="T3" s="3"/>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="5">
+        <v>47000</v>
+      </c>
+      <c r="G4" s="5">
+        <v>47000</v>
+      </c>
+      <c r="H4" s="5">
+        <v>2500</v>
+      </c>
+      <c r="I4" s="5">
+        <v>3</v>
+      </c>
+      <c r="J4" s="6">
+        <v>44359</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="L4" s="3" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M4" s="3" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N4" s="3" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O4" s="3" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P4" s="3" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="3" t="str">
+        <f t="shared" ref="R3:R21" si="6">IF(F4&lt;G4,"Got Hike","No Hike")</f>
+        <v>No Hike</v>
+      </c>
+      <c r="S4" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>Low</v>
+      </c>
+      <c r="T4" s="3"/>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="5">
+        <v>47000</v>
+      </c>
+      <c r="G5" s="5">
+        <v>47000</v>
+      </c>
+      <c r="H5" s="5">
+        <v>2600</v>
+      </c>
+      <c r="I5" s="5">
+        <v>3</v>
+      </c>
+      <c r="J5" s="6">
+        <v>44620</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="L5" s="3" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M5" s="3" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N5" s="3" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O5" s="3" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P5" s="3" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="Q5" s="3"/>
+      <c r="R5" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>No Hike</v>
+      </c>
+      <c r="S5" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>Low</v>
+      </c>
+      <c r="T5" s="3"/>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="5">
+        <v>49000</v>
+      </c>
+      <c r="G6" s="5">
+        <v>49000</v>
+      </c>
+      <c r="H6" s="5">
+        <v>2800</v>
+      </c>
+      <c r="I6" s="5">
+        <v>3</v>
+      </c>
+      <c r="J6" s="6">
+        <v>44115</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="L6" s="3" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M6" s="3" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="N6" s="3" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O6" s="3" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P6" s="3" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="Q6" s="3"/>
+      <c r="R6" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>No Hike</v>
+      </c>
+      <c r="S6" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>Low</v>
+      </c>
+      <c r="T6" s="3"/>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="5">
+        <v>48000</v>
+      </c>
+      <c r="G7" s="5">
+        <f>48000+1000</f>
+        <v>49000</v>
+      </c>
+      <c r="H7" s="5">
+        <v>3000</v>
+      </c>
+      <c r="I7" s="5">
+        <v>3</v>
+      </c>
+      <c r="J7" s="6">
+        <v>44022</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L7" s="3" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M7" s="3" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N7" s="3" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="O7" s="3" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P7" s="3" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>Got Hike</v>
+      </c>
+      <c r="S7" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>Low</v>
+      </c>
+      <c r="T7" s="3"/>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="5">
+        <v>52000</v>
+      </c>
+      <c r="G8" s="5">
+        <v>52000</v>
+      </c>
+      <c r="H8" s="5">
+        <v>3900</v>
+      </c>
+      <c r="I8" s="5">
+        <v>4</v>
+      </c>
+      <c r="J8" s="6">
+        <v>44329</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="L8" s="3" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M8" s="3" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N8" s="3" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O8" s="3" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P8" s="3" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="Q8" s="3"/>
+      <c r="R8" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>No Hike</v>
+      </c>
+      <c r="S8" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>Avg</v>
+      </c>
+      <c r="T8" s="3"/>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="5">
+        <v>51000</v>
+      </c>
+      <c r="G9" s="5">
+        <v>20000</v>
+      </c>
+      <c r="H9" s="5">
+        <v>4000</v>
+      </c>
+      <c r="I9" s="5">
+        <v>4</v>
+      </c>
+      <c r="J9" s="6">
+        <v>43886</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L9" s="3" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M9" s="3" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N9" s="3" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O9" s="3" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="P9" s="3" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q9" s="3"/>
+      <c r="R9" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>No Hike</v>
+      </c>
+      <c r="S9" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>Avg</v>
+      </c>
+      <c r="T9" s="3"/>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="5">
+        <v>53000</v>
+      </c>
+      <c r="G10" s="5">
+        <v>53000</v>
+      </c>
+      <c r="H10" s="5">
+        <v>4200</v>
+      </c>
+      <c r="I10" s="5">
+        <v>4</v>
+      </c>
+      <c r="J10" s="6">
+        <v>44531</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="L10" s="3" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M10" s="3" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N10" s="3" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O10" s="3" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P10" s="3" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="Q10" s="3"/>
+      <c r="R10" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>No Hike</v>
+      </c>
+      <c r="S10" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>Avg</v>
+      </c>
+      <c r="T10" s="3"/>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" s="5">
+        <v>54000</v>
+      </c>
+      <c r="G11" s="5">
+        <v>54000</v>
+      </c>
+      <c r="H11" s="5">
+        <v>4500</v>
+      </c>
+      <c r="I11" s="5">
+        <v>4</v>
+      </c>
+      <c r="J11" s="6">
+        <v>44566</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="L11" s="3" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M11" s="3" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N11" s="3" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O11" s="3" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P11" s="3" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>No Hike</v>
+      </c>
+      <c r="S11" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>Avg</v>
+      </c>
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="5">
+        <v>55000</v>
+      </c>
+      <c r="G12" s="5">
+        <f>55000-1000</f>
+        <v>54000</v>
+      </c>
+      <c r="H12" s="5">
+        <v>4700</v>
+      </c>
+      <c r="I12" s="5">
+        <v>4</v>
+      </c>
+      <c r="J12" s="6">
+        <v>43527</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="L12" s="3" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M12" s="3" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N12" s="3" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O12" s="3" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="P12" s="3" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q12" s="3"/>
+      <c r="R12" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>No Hike</v>
+      </c>
+      <c r="S12" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>Avg</v>
+      </c>
+      <c r="T12" s="3"/>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" s="5">
+        <v>56000</v>
+      </c>
+      <c r="G13" s="5">
+        <v>56000</v>
+      </c>
+      <c r="H13" s="5">
+        <v>4800</v>
+      </c>
+      <c r="I13" s="5">
+        <v>4</v>
+      </c>
+      <c r="J13" s="6">
+        <v>43849</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="L13" s="3" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M13" s="3" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N13" s="3" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O13" s="3" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P13" s="3" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="Q13" s="3"/>
+      <c r="R13" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>No Hike</v>
+      </c>
+      <c r="S13" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>Avg</v>
+      </c>
+      <c r="T13" s="3"/>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="5">
+        <v>52000</v>
+      </c>
+      <c r="G14" s="5">
+        <v>52000</v>
+      </c>
+      <c r="H14" s="5">
+        <v>5000</v>
+      </c>
+      <c r="I14" s="5">
+        <v>4</v>
+      </c>
+      <c r="J14" s="6">
+        <v>44270</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L14" s="3" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M14" s="3" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N14" s="3" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O14" s="3" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P14" s="3" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="Q14" s="3"/>
+      <c r="R14" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>No Hike</v>
+      </c>
+      <c r="S14" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>Avg</v>
+      </c>
+      <c r="T14" s="3"/>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F15" s="5">
+        <v>68000</v>
+      </c>
+      <c r="G15" s="5">
+        <v>68000</v>
+      </c>
+      <c r="H15" s="5">
+        <v>6000</v>
+      </c>
+      <c r="I15" s="5">
+        <v>5</v>
+      </c>
+      <c r="J15" s="6">
+        <v>43707</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="L15" s="3" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M15" s="3" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N15" s="3" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O15" s="3" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P15" s="3" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="Q15" s="3"/>
+      <c r="R15" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>No Hike</v>
+      </c>
+      <c r="S15" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>High</v>
+      </c>
+      <c r="T15" s="3"/>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F16" s="5">
+        <v>65000</v>
+      </c>
+      <c r="G16" s="5">
+        <v>65000</v>
+      </c>
+      <c r="H16" s="5">
+        <v>7000</v>
+      </c>
+      <c r="I16" s="5">
+        <v>5</v>
+      </c>
+      <c r="J16" s="6">
+        <v>43791</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L16" s="3" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M16" s="3" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N16" s="3" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O16" s="3" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P16" s="3" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>No Hike</v>
+      </c>
+      <c r="S16" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>Avg</v>
+      </c>
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="5">
+        <v>69000</v>
+      </c>
+      <c r="G17" s="5">
+        <v>69000</v>
+      </c>
+      <c r="H17" s="5">
+        <v>7100</v>
+      </c>
+      <c r="I17" s="5">
+        <v>5</v>
+      </c>
+      <c r="J17" s="6">
+        <v>43622</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="L17" s="3" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M17" s="3" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N17" s="3" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O17" s="3" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P17" s="3" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="Q17" s="3"/>
+      <c r="R17" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>No Hike</v>
+      </c>
+      <c r="S17" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>High</v>
+      </c>
+      <c r="T17" s="3"/>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F18" s="5">
+        <v>70000</v>
+      </c>
+      <c r="G18" s="5">
+        <v>70000</v>
+      </c>
+      <c r="H18" s="5">
+        <v>7500</v>
+      </c>
+      <c r="I18" s="5">
+        <v>5</v>
+      </c>
+      <c r="J18" s="6">
+        <v>43241</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="L18" s="3" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M18" s="3" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N18" s="3" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O18" s="3" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P18" s="3" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="Q18" s="3"/>
+      <c r="R18" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>No Hike</v>
+      </c>
+      <c r="S18" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>High</v>
+      </c>
+      <c r="T18" s="3"/>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F19" s="5">
+        <v>71000</v>
+      </c>
+      <c r="G19" s="5">
+        <v>71000</v>
+      </c>
+      <c r="H19" s="5">
+        <v>7800</v>
+      </c>
+      <c r="I19" s="5">
+        <v>5</v>
+      </c>
+      <c r="J19" s="6">
+        <v>43458</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="L19" s="3" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M19" s="3" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N19" s="3" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O19" s="3" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P19" s="3" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>No Hike</v>
+      </c>
+      <c r="S19" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>High</v>
+      </c>
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" s="5">
+        <v>72000</v>
+      </c>
+      <c r="G20" s="5">
+        <v>72000</v>
+      </c>
+      <c r="H20" s="5">
+        <v>8000</v>
+      </c>
+      <c r="I20" s="5">
+        <v>5</v>
+      </c>
+      <c r="J20" s="6">
+        <v>43361</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="L20" s="3" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M20" s="3" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N20" s="3" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O20" s="3" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P20" s="3" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="Q20" s="3"/>
+      <c r="R20" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>No Hike</v>
+      </c>
+      <c r="S20" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>High</v>
+      </c>
+      <c r="T20" s="3"/>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F21" s="5">
+        <v>73000</v>
+      </c>
+      <c r="G21" s="5">
+        <v>73000</v>
+      </c>
+      <c r="H21" s="5">
+        <v>8200</v>
+      </c>
+      <c r="I21" s="5">
+        <v>5</v>
+      </c>
+      <c r="J21" s="6">
+        <v>42930</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="L21" s="3" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M21" s="3" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N21" s="3" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O21" s="3" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P21" s="3" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="Q21" s="3"/>
+      <c r="R21" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>No Hike</v>
+      </c>
+      <c r="S21" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>High</v>
+      </c>
+      <c r="T21" s="3"/>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="F22" s="2">
+        <f>SUM(F2:F21)</f>
+        <v>1143000</v>
+      </c>
+      <c r="G22" s="2">
+        <f>SUM(G2:G21)</f>
+        <v>1151000</v>
+      </c>
+      <c r="H22" s="2">
+        <f>SUM(H2:H21)</f>
+        <v>97800</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:Z22"/>
+  <conditionalFormatting sqref="U1:U21">
+    <cfRule type="containsText" dxfId="14" priority="6" operator="containsText" text="TRUE">
+      <formula>NOT(ISERROR(SEARCH("TRUE",U1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="13" priority="7" operator="containsText" text="FALSE">
+      <formula>NOT(ISERROR(SEARCH("FALSE",U1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L21">
+    <cfRule type="cellIs" dxfId="12" priority="5" operator="equal">
+      <formula>FALSE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M2:M21">
+    <cfRule type="cellIs" dxfId="11" priority="4" operator="equal">
+      <formula>FALSE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N2:N21">
+    <cfRule type="cellIs" dxfId="10" priority="3" operator="equal">
+      <formula>FALSE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O2:O21">
+    <cfRule type="cellIs" dxfId="9" priority="2" operator="equal">
+      <formula>FALSE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P2:P21">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
+      <formula>FALSE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="K14" r:id="rId1" display="mailto:john.smith@email.com"/>
+    <hyperlink ref="K7" r:id="rId2" display="mailto:sara.khan@email.com"/>
+    <hyperlink ref="K16" r:id="rId3" display="mailto:mike.j@email.com"/>
+    <hyperlink ref="K11" r:id="rId4" display="mailto:emily.d@email.com"/>
+    <hyperlink ref="K20" r:id="rId5" display="mailto:raj.patel@email.com"/>
+    <hyperlink ref="K4" r:id="rId6" display="mailto:anna.lee@email.com"/>
+    <hyperlink ref="K9" r:id="rId7" display="mailto:chris.b@email.com"/>
+    <hyperlink ref="K15" r:id="rId8" display="mailto:david.w@email.com"/>
+    <hyperlink ref="K2" r:id="rId9" display="mailto:lisa.t@email.com"/>
+    <hyperlink ref="K10" r:id="rId10" display="mailto:tom.a@email.com"/>
+    <hyperlink ref="K18" r:id="rId11" display="mailto:nina.g@email.com"/>
+    <hyperlink ref="K6" r:id="rId12" display="mailto:alex.m@email.com"/>
+    <hyperlink ref="K12" r:id="rId13" display="mailto:kevin.w@email.com"/>
+    <hyperlink ref="K21" r:id="rId14" display="mailto:priya.s@email.com"/>
+    <hyperlink ref="K3" r:id="rId15" display="mailto:daniel.c@email.com"/>
+    <hyperlink ref="K13" r:id="rId16" display="mailto:sophia.l@email.com"/>
+    <hyperlink ref="K17" r:id="rId17" display="mailto:james.w@email.com"/>
+    <hyperlink ref="K5" r:id="rId18" display="mailto:olivia.h@email.com"/>
+    <hyperlink ref="K8" r:id="rId19" display="mailto:ethan.a@email.com"/>
+    <hyperlink ref="K19" r:id="rId20" display="mailto:chloe.y@email.com"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId21"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2067,7 +3769,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:V29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/17 18 20/Excel/4.Advanced Tools & Automation/4.LogicalFunctions/Logical_Functions.xlsx
+++ b/17 18 20/Excel/4.Advanced Tools & Automation/4.LogicalFunctions/Logical_Functions.xlsx
@@ -12,12 +12,15 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072"/>
   </bookViews>
   <sheets>
-    <sheet name="ComparisonOperator (2)" sheetId="20" r:id="rId1"/>
-    <sheet name="ComparisonOperator" sheetId="13" r:id="rId2"/>
-    <sheet name="ConditionalFunctions" sheetId="19" r:id="rId3"/>
+    <sheet name="ComparisonOperator" sheetId="13" r:id="rId1"/>
+    <sheet name="IF , NestedIF" sheetId="20" r:id="rId2"/>
+    <sheet name="AND OR NOT" sheetId="21" r:id="rId3"/>
+    <sheet name="IFERROR" sheetId="22" r:id="rId4"/>
+    <sheet name="ConditionalFunctions" sheetId="19" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ComparisonOperator (2)'!$A$1:$Z$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'AND OR NOT'!$A$3:$L$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'IF , NestedIF'!$A$2:$K$23</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="132">
   <si>
     <t>EmpID</t>
   </si>
@@ -379,10 +382,52 @@
     <t>Alex Martineez</t>
   </si>
   <si>
-    <t>if(logic,value_True,Value_False)</t>
-  </si>
-  <si>
-    <t>=IF(LOGItES,VALUE_TRUE,VALUE_IFfALSE)</t>
+    <t>below 3000</t>
+  </si>
+  <si>
+    <t>below 5000</t>
+  </si>
+  <si>
+    <t>rest</t>
+  </si>
+  <si>
+    <t>Sale</t>
+  </si>
+  <si>
+    <t>incentives</t>
+  </si>
+  <si>
+    <t>asdf</t>
+  </si>
+  <si>
+    <t>And</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logic_01, </t>
+  </si>
+  <si>
+    <t>Logic_2</t>
+  </si>
+  <si>
+    <t>After Appraisal</t>
+  </si>
+  <si>
+    <t>Comparison Operator</t>
+  </si>
+  <si>
+    <t>=AND(logic_1,Logic_2,Logic_3……………..)</t>
+  </si>
+  <si>
+    <t>=OR(logic_1,Logic_2,Logic_3……………..)</t>
+  </si>
+  <si>
+    <t>if Error with Vlookup</t>
+  </si>
+  <si>
+    <t>If Error with Remarks</t>
+  </si>
+  <si>
+    <t>IF Logic</t>
   </si>
 </sst>
 </file>
@@ -393,7 +438,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -439,14 +484,60 @@
     </font>
     <font>
       <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Candara"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Candara"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Candara"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Candara"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF00B050"/>
+      <name val="Candara"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Candara"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -459,8 +550,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -496,13 +593,43 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -559,19 +686,87 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
+    <cellStyle name="60% - Accent5" xfId="3" builtinId="48"/>
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="24">
+  <dxfs count="15">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -634,11 +829,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -714,101 +909,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1088,1486 +1193,1383 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z22"/>
+  <dimension ref="A1:R23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.77734375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="5.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="17" width="10.77734375" style="2" hidden="1" customWidth="1"/>
-    <col min="18" max="18" width="26.5546875" style="2" customWidth="1"/>
-    <col min="19" max="19" width="27" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="37.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="2.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="4.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="3.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="4.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="8.88671875" style="2"/>
+    <col min="3" max="3" width="5.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.77734375" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.21875" style="8" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.109375" style="2" customWidth="1"/>
+    <col min="12" max="15" width="6" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="6" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="4" t="s">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="L1" s="39" t="s">
+        <v>126</v>
+      </c>
+      <c r="M1" s="39"/>
+      <c r="N1" s="39"/>
+      <c r="O1" s="39"/>
+      <c r="P1" s="39"/>
+      <c r="Q1" s="39"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="H1" s="4" t="s">
+      <c r="E2" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="25" t="s">
+        <v>125</v>
+      </c>
+      <c r="G2" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="H2" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="I2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="J2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="K2" s="1"/>
+      <c r="L2" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="Z1" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B3" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="D2" s="5" t="s">
+      <c r="C3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="D3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="5">
+      <c r="E3" s="26">
         <v>46000</v>
       </c>
-      <c r="G2" s="5">
+      <c r="F3" s="26">
+        <v>51000</v>
+      </c>
+      <c r="G3" s="26">
+        <v>2000</v>
+      </c>
+      <c r="H3" s="26">
+        <v>2</v>
+      </c>
+      <c r="I3" s="6">
+        <v>44668</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="K3" s="3"/>
+      <c r="L3" s="27" t="b">
+        <f>E3=F3</f>
+        <v>0</v>
+      </c>
+      <c r="M3" s="27" t="b">
+        <f>E3&lt;&gt;F3</f>
+        <v>1</v>
+      </c>
+      <c r="N3" s="27" t="b">
+        <f>E3&lt;F3</f>
+        <v>1</v>
+      </c>
+      <c r="O3" s="27" t="b">
+        <f>E3&gt;F3</f>
+        <v>0</v>
+      </c>
+      <c r="P3" s="27" t="b">
+        <f>E3&lt;=F3</f>
+        <v>1</v>
+      </c>
+      <c r="Q3" s="27" t="b">
+        <f>E3&gt;=F3</f>
+        <v>0</v>
+      </c>
+      <c r="R3" s="27" t="b">
+        <f>NOT(E3&gt;=F3)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="26">
+        <v>45000</v>
+      </c>
+      <c r="F4" s="26">
         <v>50000</v>
       </c>
-      <c r="H2" s="5">
-        <v>2000</v>
-      </c>
-      <c r="I2" s="5">
+      <c r="G4" s="26">
+        <v>2200</v>
+      </c>
+      <c r="H4" s="26">
         <v>2</v>
       </c>
-      <c r="J2" s="6">
-        <v>44668</v>
-      </c>
-      <c r="K2" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="L2" s="3" t="b">
-        <f>B2=C2</f>
-        <v>0</v>
-      </c>
-      <c r="M2" s="3" t="b">
-        <f>B2&lt;&gt;C2</f>
-        <v>1</v>
-      </c>
-      <c r="N2" s="3" t="b">
-        <f>F2&lt;G2</f>
-        <v>1</v>
-      </c>
-      <c r="O2" s="3" t="b">
-        <f>F2&gt;G2</f>
-        <v>0</v>
-      </c>
-      <c r="P2" s="3" t="b">
-        <f>F2&lt;=G2</f>
-        <v>1</v>
-      </c>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3" t="str">
-        <f>IF(F2&lt;G2,"Got Hike","No Hike")</f>
-        <v>Got Hike</v>
-      </c>
-      <c r="S2" s="2" t="str">
-        <f>IF(F2&lt;51000,"Low",IF(F2&lt;68000,"Avg","High"))</f>
-        <v>Low</v>
-      </c>
-      <c r="T2" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="W2" s="22" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="D3" s="5" t="s">
+      <c r="I4" s="6">
+        <v>44448</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="K4" s="3"/>
+      <c r="L4" s="27" t="b">
+        <f t="shared" ref="L4:L22" si="0">E4=F4</f>
+        <v>0</v>
+      </c>
+      <c r="M4" s="27" t="b">
+        <f t="shared" ref="M4:M22" si="1">E4&lt;&gt;F4</f>
+        <v>1</v>
+      </c>
+      <c r="N4" s="27" t="b">
+        <f t="shared" ref="N4:N22" si="2">E4&lt;F4</f>
+        <v>1</v>
+      </c>
+      <c r="O4" s="27" t="b">
+        <f t="shared" ref="O4:O22" si="3">E4&gt;F4</f>
+        <v>0</v>
+      </c>
+      <c r="P4" s="27" t="b">
+        <f>E4&lt;=F4</f>
+        <v>1</v>
+      </c>
+      <c r="Q4" s="27" t="b">
+        <f>E4&gt;=F4</f>
+        <v>0</v>
+      </c>
+      <c r="R4" s="27" t="b">
+        <f t="shared" ref="R4:R22" si="4">NOT(E4&gt;=F4)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="D5" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="26">
+        <v>47000</v>
+      </c>
+      <c r="F5" s="26">
+        <v>52000</v>
+      </c>
+      <c r="G5" s="26">
+        <v>2500</v>
+      </c>
+      <c r="H5" s="26">
+        <v>3</v>
+      </c>
+      <c r="I5" s="6">
+        <v>44359</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="K5" s="3"/>
+      <c r="L5" s="27" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M5" s="27" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="N5" s="27" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="O5" s="27" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P5" s="27" t="b">
+        <f t="shared" ref="P5:P22" si="5">E5&lt;=F5</f>
+        <v>1</v>
+      </c>
+      <c r="Q5" s="27" t="b">
+        <f t="shared" ref="Q5:Q22" si="6">E5&gt;=F5</f>
+        <v>0</v>
+      </c>
+      <c r="R5" s="27" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="26">
+        <v>47000</v>
+      </c>
+      <c r="F6" s="26">
+        <v>47000</v>
+      </c>
+      <c r="G6" s="26">
+        <v>2600</v>
+      </c>
+      <c r="H6" s="26">
+        <v>3</v>
+      </c>
+      <c r="I6" s="6">
+        <v>44620</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="K6" s="3"/>
+      <c r="L6" s="27" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M6" s="27" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N6" s="27" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O6" s="27" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P6" s="27" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="Q6" s="27" t="b">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="R6" s="27" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="26">
+        <v>49000</v>
+      </c>
+      <c r="F7" s="26">
+        <v>54000</v>
+      </c>
+      <c r="G7" s="26">
+        <v>2800</v>
+      </c>
+      <c r="H7" s="26">
+        <v>3</v>
+      </c>
+      <c r="I7" s="6">
+        <v>44115</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="K7" s="3"/>
+      <c r="L7" s="27" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M7" s="27" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="N7" s="27" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="O7" s="27" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P7" s="27" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="Q7" s="27" t="b">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="R7" s="27" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="5">
-        <v>45000</v>
-      </c>
-      <c r="G3" s="5">
-        <v>80000</v>
-      </c>
-      <c r="H3" s="5">
-        <v>2200</v>
-      </c>
-      <c r="I3" s="5">
-        <v>2</v>
-      </c>
-      <c r="J3" s="6">
-        <v>44448</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="L3" s="3" t="b">
-        <f t="shared" ref="L3:L21" si="0">B3=C3</f>
-        <v>1</v>
-      </c>
-      <c r="M3" s="3" t="b">
-        <f t="shared" ref="M3:M21" si="1">B3&lt;&gt;C3</f>
-        <v>0</v>
-      </c>
-      <c r="N3" s="3" t="b">
-        <f t="shared" ref="N3:N21" si="2">F3&lt;G3</f>
-        <v>1</v>
-      </c>
-      <c r="O3" s="3" t="b">
-        <f t="shared" ref="O3:O21" si="3">F3&gt;G3</f>
-        <v>0</v>
-      </c>
-      <c r="P3" s="3" t="b">
-        <f t="shared" ref="P3:P21" si="4">F3&lt;=G3</f>
-        <v>1</v>
-      </c>
-      <c r="Q3" s="3"/>
-      <c r="R3" s="3" t="str">
-        <f>IF(F3&lt;G3,"Got Hike","No Hike")</f>
-        <v>Got Hike</v>
-      </c>
-      <c r="S3" s="2" t="str">
-        <f t="shared" ref="S3:S21" si="5">IF(F3&lt;51000,"Low",IF(F3&lt;68000,"Avg","High"))</f>
-        <v>Low</v>
-      </c>
-      <c r="T3" s="3"/>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="5" t="s">
+      <c r="E8" s="26">
+        <v>48000</v>
+      </c>
+      <c r="F8" s="26">
+        <v>53000</v>
+      </c>
+      <c r="G8" s="26">
+        <v>3000</v>
+      </c>
+      <c r="H8" s="26">
+        <v>3</v>
+      </c>
+      <c r="I8" s="6">
+        <v>44022</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="K8" s="3"/>
+      <c r="L8" s="27" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M8" s="27" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="N8" s="27" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="O8" s="27" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P8" s="27" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="Q8" s="27" t="b">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="R8" s="27" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="26">
+        <v>52000</v>
+      </c>
+      <c r="F9" s="26">
+        <v>57000</v>
+      </c>
+      <c r="G9" s="26">
+        <v>3900</v>
+      </c>
+      <c r="H9" s="26">
+        <v>4</v>
+      </c>
+      <c r="I9" s="6">
+        <v>44329</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="K9" s="3"/>
+      <c r="L9" s="27" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M9" s="27" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="N9" s="27" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="O9" s="27" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P9" s="27" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="Q9" s="27" t="b">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="R9" s="27" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="26">
+        <v>51000</v>
+      </c>
+      <c r="F10" s="26">
+        <v>56000</v>
+      </c>
+      <c r="G10" s="26">
+        <v>4000</v>
+      </c>
+      <c r="H10" s="26">
+        <v>4</v>
+      </c>
+      <c r="I10" s="6">
+        <v>43886</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="K10" s="3"/>
+      <c r="L10" s="27" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M10" s="27" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="N10" s="27" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="O10" s="27" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P10" s="27" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="Q10" s="27" t="b">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="R10" s="27" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="5">
-        <v>47000</v>
-      </c>
-      <c r="G4" s="5">
-        <v>47000</v>
-      </c>
-      <c r="H4" s="5">
-        <v>2500</v>
-      </c>
-      <c r="I4" s="5">
-        <v>3</v>
-      </c>
-      <c r="J4" s="6">
-        <v>44359</v>
-      </c>
-      <c r="K4" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="L4" s="3" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M4" s="3" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N4" s="3" t="b">
+      <c r="E11" s="26">
+        <v>53000</v>
+      </c>
+      <c r="F11" s="26">
+        <v>53000</v>
+      </c>
+      <c r="G11" s="26">
+        <v>4200</v>
+      </c>
+      <c r="H11" s="26">
+        <v>4</v>
+      </c>
+      <c r="I11" s="6">
+        <v>44531</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="K11" s="3"/>
+      <c r="L11" s="27" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M11" s="27" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N11" s="27" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O4" s="3" t="b">
+      <c r="O11" s="27" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P4" s="3" t="b">
+      <c r="P11" s="27" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="Q11" s="27" t="b">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="R11" s="27" t="b">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="Q4" s="3"/>
-      <c r="R4" s="3" t="str">
-        <f t="shared" ref="R3:R21" si="6">IF(F4&lt;G4,"Got Hike","No Hike")</f>
-        <v>No Hike</v>
-      </c>
-      <c r="S4" s="2" t="str">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" s="26">
+        <v>54000</v>
+      </c>
+      <c r="F12" s="26">
+        <v>59000</v>
+      </c>
+      <c r="G12" s="26">
+        <v>4500</v>
+      </c>
+      <c r="H12" s="26">
+        <v>4</v>
+      </c>
+      <c r="I12" s="6">
+        <v>44566</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="K12" s="3"/>
+      <c r="L12" s="27" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M12" s="27" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="N12" s="27" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="O12" s="27" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P12" s="27" t="b">
         <f t="shared" si="5"/>
-        <v>Low</v>
-      </c>
-      <c r="T4" s="3"/>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="27" t="b">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="R12" s="27" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="26">
+        <v>55000</v>
+      </c>
+      <c r="F13" s="26">
+        <v>60000</v>
+      </c>
+      <c r="G13" s="26">
+        <v>4700</v>
+      </c>
+      <c r="H13" s="26">
+        <v>4</v>
+      </c>
+      <c r="I13" s="6">
+        <v>43527</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="K13" s="3"/>
+      <c r="L13" s="27" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M13" s="27" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="N13" s="27" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="O13" s="27" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P13" s="27" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="Q13" s="27" t="b">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="R13" s="27" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" s="26">
+        <v>56000</v>
+      </c>
+      <c r="F14" s="26">
+        <v>61000</v>
+      </c>
+      <c r="G14" s="26">
+        <v>4800</v>
+      </c>
+      <c r="H14" s="26">
+        <v>4</v>
+      </c>
+      <c r="I14" s="6">
+        <v>43849</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="K14" s="3"/>
+      <c r="L14" s="27" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M14" s="27" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="N14" s="27" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="O14" s="27" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P14" s="27" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="Q14" s="27" t="b">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="R14" s="27" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" s="26">
+        <v>52000</v>
+      </c>
+      <c r="F15" s="26">
+        <v>57000</v>
+      </c>
+      <c r="G15" s="26">
+        <v>5000</v>
+      </c>
+      <c r="H15" s="26">
+        <v>4</v>
+      </c>
+      <c r="I15" s="6">
+        <v>44270</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K15" s="3"/>
+      <c r="L15" s="27" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M15" s="27" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="N15" s="27" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="O15" s="27" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P15" s="27" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="Q15" s="27" t="b">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="R15" s="27" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="26">
+        <v>68000</v>
+      </c>
+      <c r="F16" s="26">
+        <v>68000</v>
+      </c>
+      <c r="G16" s="26">
+        <v>6000</v>
+      </c>
+      <c r="H16" s="26">
+        <v>5</v>
+      </c>
+      <c r="I16" s="6">
+        <v>43707</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="K16" s="3"/>
+      <c r="L16" s="27" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M16" s="27" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N16" s="27" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O16" s="27" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P16" s="27" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="Q16" s="27" t="b">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="R16" s="27" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="5">
-        <v>47000</v>
-      </c>
-      <c r="G5" s="5">
-        <v>47000</v>
-      </c>
-      <c r="H5" s="5">
-        <v>2600</v>
-      </c>
-      <c r="I5" s="5">
-        <v>3</v>
-      </c>
-      <c r="J5" s="6">
-        <v>44620</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="L5" s="3" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M5" s="3" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N5" s="3" t="b">
+      <c r="E17" s="26">
+        <v>65000</v>
+      </c>
+      <c r="F17" s="26">
+        <v>65000</v>
+      </c>
+      <c r="G17" s="26">
+        <v>7000</v>
+      </c>
+      <c r="H17" s="26">
+        <v>5</v>
+      </c>
+      <c r="I17" s="6">
+        <v>43791</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K17" s="3"/>
+      <c r="L17" s="27" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M17" s="27" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N17" s="27" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O5" s="3" t="b">
+      <c r="O17" s="27" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P5" s="3" t="b">
+      <c r="P17" s="27" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="Q17" s="27" t="b">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="R17" s="27" t="b">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="3" t="str">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" s="26">
+        <v>69000</v>
+      </c>
+      <c r="F18" s="26">
+        <v>69000</v>
+      </c>
+      <c r="G18" s="26">
+        <v>7100</v>
+      </c>
+      <c r="H18" s="26">
+        <v>5</v>
+      </c>
+      <c r="I18" s="6">
+        <v>43622</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="K18" s="3"/>
+      <c r="L18" s="27" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M18" s="27" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N18" s="27" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O18" s="27" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P18" s="27" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="Q18" s="27" t="b">
         <f t="shared" si="6"/>
-        <v>No Hike</v>
-      </c>
-      <c r="S5" s="2" t="str">
+        <v>1</v>
+      </c>
+      <c r="R18" s="27" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E19" s="26">
+        <v>70000</v>
+      </c>
+      <c r="F19" s="26">
+        <v>70000</v>
+      </c>
+      <c r="G19" s="26">
+        <v>7500</v>
+      </c>
+      <c r="H19" s="26">
+        <v>5</v>
+      </c>
+      <c r="I19" s="6">
+        <v>43241</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="K19" s="3"/>
+      <c r="L19" s="27" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M19" s="27" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N19" s="27" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O19" s="27" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P19" s="27" t="b">
         <f t="shared" si="5"/>
-        <v>Low</v>
-      </c>
-      <c r="T5" s="3"/>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="27" t="b">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="R19" s="27" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F6" s="5">
-        <v>49000</v>
-      </c>
-      <c r="G6" s="5">
-        <v>49000</v>
-      </c>
-      <c r="H6" s="5">
-        <v>2800</v>
-      </c>
-      <c r="I6" s="5">
-        <v>3</v>
-      </c>
-      <c r="J6" s="6">
-        <v>44115</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="L6" s="3" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M6" s="3" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="N6" s="3" t="b">
+      <c r="E20" s="26">
+        <v>71000</v>
+      </c>
+      <c r="F20" s="26">
+        <v>71000</v>
+      </c>
+      <c r="G20" s="26">
+        <v>7800</v>
+      </c>
+      <c r="H20" s="26">
+        <v>5</v>
+      </c>
+      <c r="I20" s="6">
+        <v>43458</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="K20" s="3"/>
+      <c r="L20" s="27" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M20" s="27" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N20" s="27" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O6" s="3" t="b">
+      <c r="O20" s="27" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P6" s="3" t="b">
+      <c r="P20" s="27" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="Q20" s="27" t="b">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="R20" s="27" t="b">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="3" t="str">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21" s="26">
+        <v>72000</v>
+      </c>
+      <c r="F21" s="26">
+        <v>77000</v>
+      </c>
+      <c r="G21" s="26">
+        <v>8000</v>
+      </c>
+      <c r="H21" s="26">
+        <v>5</v>
+      </c>
+      <c r="I21" s="6">
+        <v>43361</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="K21" s="3"/>
+      <c r="L21" s="27" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M21" s="27" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="N21" s="27" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="O21" s="27" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P21" s="27" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="Q21" s="27" t="b">
         <f t="shared" si="6"/>
-        <v>No Hike</v>
-      </c>
-      <c r="S6" s="2" t="str">
+        <v>0</v>
+      </c>
+      <c r="R21" s="27" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E22" s="26">
+        <v>73000</v>
+      </c>
+      <c r="F22" s="26">
+        <v>78000</v>
+      </c>
+      <c r="G22" s="26">
+        <v>8200</v>
+      </c>
+      <c r="H22" s="26">
+        <v>5</v>
+      </c>
+      <c r="I22" s="6">
+        <v>42930</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="K22" s="3"/>
+      <c r="L22" s="27" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M22" s="27" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="N22" s="27" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="O22" s="27" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P22" s="27" t="b">
         <f t="shared" si="5"/>
-        <v>Low</v>
-      </c>
-      <c r="T6" s="3"/>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="5">
-        <v>48000</v>
-      </c>
-      <c r="G7" s="5">
-        <f>48000+1000</f>
-        <v>49000</v>
-      </c>
-      <c r="H7" s="5">
-        <v>3000</v>
-      </c>
-      <c r="I7" s="5">
-        <v>3</v>
-      </c>
-      <c r="J7" s="6">
-        <v>44022</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="L7" s="3" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M7" s="3" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N7" s="3" t="b">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="O7" s="3" t="b">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P7" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q22" s="27" t="b">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="R22" s="27" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="Q7" s="3"/>
-      <c r="R7" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>Got Hike</v>
-      </c>
-      <c r="S7" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>Low</v>
-      </c>
-      <c r="T7" s="3"/>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" s="5">
-        <v>52000</v>
-      </c>
-      <c r="G8" s="5">
-        <v>52000</v>
-      </c>
-      <c r="H8" s="5">
-        <v>3900</v>
-      </c>
-      <c r="I8" s="5">
-        <v>4</v>
-      </c>
-      <c r="J8" s="6">
-        <v>44329</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="L8" s="3" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M8" s="3" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N8" s="3" t="b">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O8" s="3" t="b">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P8" s="3" t="b">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="Q8" s="3"/>
-      <c r="R8" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>No Hike</v>
-      </c>
-      <c r="S8" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>Avg</v>
-      </c>
-      <c r="T8" s="3"/>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9" s="5">
-        <v>51000</v>
-      </c>
-      <c r="G9" s="5">
-        <v>20000</v>
-      </c>
-      <c r="H9" s="5">
-        <v>4000</v>
-      </c>
-      <c r="I9" s="5">
-        <v>4</v>
-      </c>
-      <c r="J9" s="6">
-        <v>43886</v>
-      </c>
-      <c r="K9" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="L9" s="3" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M9" s="3" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N9" s="3" t="b">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O9" s="3" t="b">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="P9" s="3" t="b">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>No Hike</v>
-      </c>
-      <c r="S9" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>Avg</v>
-      </c>
-      <c r="T9" s="3"/>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F10" s="5">
-        <v>53000</v>
-      </c>
-      <c r="G10" s="5">
-        <v>53000</v>
-      </c>
-      <c r="H10" s="5">
-        <v>4200</v>
-      </c>
-      <c r="I10" s="5">
-        <v>4</v>
-      </c>
-      <c r="J10" s="6">
-        <v>44531</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="L10" s="3" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M10" s="3" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N10" s="3" t="b">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O10" s="3" t="b">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P10" s="3" t="b">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="Q10" s="3"/>
-      <c r="R10" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>No Hike</v>
-      </c>
-      <c r="S10" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>Avg</v>
-      </c>
-      <c r="T10" s="3"/>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F11" s="5">
-        <v>54000</v>
-      </c>
-      <c r="G11" s="5">
-        <v>54000</v>
-      </c>
-      <c r="H11" s="5">
-        <v>4500</v>
-      </c>
-      <c r="I11" s="5">
-        <v>4</v>
-      </c>
-      <c r="J11" s="6">
-        <v>44566</v>
-      </c>
-      <c r="K11" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L11" s="3" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M11" s="3" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N11" s="3" t="b">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O11" s="3" t="b">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P11" s="3" t="b">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="Q11" s="3"/>
-      <c r="R11" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>No Hike</v>
-      </c>
-      <c r="S11" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>Avg</v>
-      </c>
-      <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" s="5">
-        <v>55000</v>
-      </c>
-      <c r="G12" s="5">
-        <f>55000-1000</f>
-        <v>54000</v>
-      </c>
-      <c r="H12" s="5">
-        <v>4700</v>
-      </c>
-      <c r="I12" s="5">
-        <v>4</v>
-      </c>
-      <c r="J12" s="6">
-        <v>43527</v>
-      </c>
-      <c r="K12" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="L12" s="3" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M12" s="3" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N12" s="3" t="b">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O12" s="3" t="b">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="P12" s="3" t="b">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Q12" s="3"/>
-      <c r="R12" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>No Hike</v>
-      </c>
-      <c r="S12" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>Avg</v>
-      </c>
-      <c r="T12" s="3"/>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F13" s="5">
-        <v>56000</v>
-      </c>
-      <c r="G13" s="5">
-        <v>56000</v>
-      </c>
-      <c r="H13" s="5">
-        <v>4800</v>
-      </c>
-      <c r="I13" s="5">
-        <v>4</v>
-      </c>
-      <c r="J13" s="6">
-        <v>43849</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="L13" s="3" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M13" s="3" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N13" s="3" t="b">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O13" s="3" t="b">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P13" s="3" t="b">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="Q13" s="3"/>
-      <c r="R13" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>No Hike</v>
-      </c>
-      <c r="S13" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>Avg</v>
-      </c>
-      <c r="T13" s="3"/>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" s="5">
-        <v>52000</v>
-      </c>
-      <c r="G14" s="5">
-        <v>52000</v>
-      </c>
-      <c r="H14" s="5">
-        <v>5000</v>
-      </c>
-      <c r="I14" s="5">
-        <v>4</v>
-      </c>
-      <c r="J14" s="6">
-        <v>44270</v>
-      </c>
-      <c r="K14" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="L14" s="3" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M14" s="3" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="b">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O14" s="3" t="b">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P14" s="3" t="b">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="Q14" s="3"/>
-      <c r="R14" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>No Hike</v>
-      </c>
-      <c r="S14" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>Avg</v>
-      </c>
-      <c r="T14" s="3"/>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A15" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F15" s="5">
-        <v>68000</v>
-      </c>
-      <c r="G15" s="5">
-        <v>68000</v>
-      </c>
-      <c r="H15" s="5">
-        <v>6000</v>
-      </c>
-      <c r="I15" s="5">
-        <v>5</v>
-      </c>
-      <c r="J15" s="6">
-        <v>43707</v>
-      </c>
-      <c r="K15" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="L15" s="3" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M15" s="3" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N15" s="3" t="b">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O15" s="3" t="b">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P15" s="3" t="b">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="Q15" s="3"/>
-      <c r="R15" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>No Hike</v>
-      </c>
-      <c r="S15" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>High</v>
-      </c>
-      <c r="T15" s="3"/>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F16" s="5">
-        <v>65000</v>
-      </c>
-      <c r="G16" s="5">
-        <v>65000</v>
-      </c>
-      <c r="H16" s="5">
-        <v>7000</v>
-      </c>
-      <c r="I16" s="5">
-        <v>5</v>
-      </c>
-      <c r="J16" s="6">
-        <v>43791</v>
-      </c>
-      <c r="K16" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="L16" s="3" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M16" s="3" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N16" s="3" t="b">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O16" s="3" t="b">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P16" s="3" t="b">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="Q16" s="3"/>
-      <c r="R16" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>No Hike</v>
-      </c>
-      <c r="S16" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>Avg</v>
-      </c>
-      <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A17" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" s="5">
-        <v>69000</v>
-      </c>
-      <c r="G17" s="5">
-        <v>69000</v>
-      </c>
-      <c r="H17" s="5">
-        <v>7100</v>
-      </c>
-      <c r="I17" s="5">
-        <v>5</v>
-      </c>
-      <c r="J17" s="6">
-        <v>43622</v>
-      </c>
-      <c r="K17" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="L17" s="3" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M17" s="3" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N17" s="3" t="b">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O17" s="3" t="b">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P17" s="3" t="b">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="Q17" s="3"/>
-      <c r="R17" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>No Hike</v>
-      </c>
-      <c r="S17" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>High</v>
-      </c>
-      <c r="T17" s="3"/>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A18" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F18" s="5">
-        <v>70000</v>
-      </c>
-      <c r="G18" s="5">
-        <v>70000</v>
-      </c>
-      <c r="H18" s="5">
-        <v>7500</v>
-      </c>
-      <c r="I18" s="5">
-        <v>5</v>
-      </c>
-      <c r="J18" s="6">
-        <v>43241</v>
-      </c>
-      <c r="K18" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="L18" s="3" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M18" s="3" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N18" s="3" t="b">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O18" s="3" t="b">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P18" s="3" t="b">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="Q18" s="3"/>
-      <c r="R18" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>No Hike</v>
-      </c>
-      <c r="S18" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>High</v>
-      </c>
-      <c r="T18" s="3"/>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A19" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F19" s="5">
-        <v>71000</v>
-      </c>
-      <c r="G19" s="5">
-        <v>71000</v>
-      </c>
-      <c r="H19" s="5">
-        <v>7800</v>
-      </c>
-      <c r="I19" s="5">
-        <v>5</v>
-      </c>
-      <c r="J19" s="6">
-        <v>43458</v>
-      </c>
-      <c r="K19" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="L19" s="3" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M19" s="3" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N19" s="3" t="b">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O19" s="3" t="b">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P19" s="3" t="b">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="Q19" s="3"/>
-      <c r="R19" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>No Hike</v>
-      </c>
-      <c r="S19" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>High</v>
-      </c>
-      <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A20" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F20" s="5">
-        <v>72000</v>
-      </c>
-      <c r="G20" s="5">
-        <v>72000</v>
-      </c>
-      <c r="H20" s="5">
-        <v>8000</v>
-      </c>
-      <c r="I20" s="5">
-        <v>5</v>
-      </c>
-      <c r="J20" s="6">
-        <v>43361</v>
-      </c>
-      <c r="K20" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="L20" s="3" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M20" s="3" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N20" s="3" t="b">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O20" s="3" t="b">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P20" s="3" t="b">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="Q20" s="3"/>
-      <c r="R20" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>No Hike</v>
-      </c>
-      <c r="S20" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>High</v>
-      </c>
-      <c r="T20" s="3"/>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A21" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F21" s="5">
-        <v>73000</v>
-      </c>
-      <c r="G21" s="5">
-        <v>73000</v>
-      </c>
-      <c r="H21" s="5">
-        <v>8200</v>
-      </c>
-      <c r="I21" s="5">
-        <v>5</v>
-      </c>
-      <c r="J21" s="6">
-        <v>42930</v>
-      </c>
-      <c r="K21" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="L21" s="3" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M21" s="3" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N21" s="3" t="b">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O21" s="3" t="b">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P21" s="3" t="b">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="Q21" s="3"/>
-      <c r="R21" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>No Hike</v>
-      </c>
-      <c r="S21" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v>High</v>
-      </c>
-      <c r="T21" s="3"/>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="F22" s="2">
-        <f>SUM(F2:F21)</f>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="E23" s="8">
+        <f>SUM(E3:E22)</f>
         <v>1143000</v>
       </c>
-      <c r="G22" s="2">
-        <f>SUM(G2:G21)</f>
-        <v>1151000</v>
-      </c>
-      <c r="H22" s="2">
-        <f>SUM(H2:H21)</f>
+      <c r="G23" s="8">
+        <f>SUM(G3:G22)</f>
         <v>97800</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Z22"/>
-  <conditionalFormatting sqref="U1:U21">
-    <cfRule type="containsText" dxfId="14" priority="6" operator="containsText" text="TRUE">
-      <formula>NOT(ISERROR(SEARCH("TRUE",U1)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="13" priority="7" operator="containsText" text="FALSE">
-      <formula>NOT(ISERROR(SEARCH("FALSE",U1)))</formula>
+  <sortState ref="A2:J21">
+    <sortCondition ref="G2:G21"/>
+  </sortState>
+  <mergeCells count="1">
+    <mergeCell ref="L1:Q1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="L3:L22">
+    <cfRule type="cellIs" dxfId="14" priority="7" operator="equal">
+      <formula>FALSE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L21">
+  <conditionalFormatting sqref="M3:M22">
+    <cfRule type="cellIs" dxfId="13" priority="6" operator="equal">
+      <formula>FALSE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N3:N22">
     <cfRule type="cellIs" dxfId="12" priority="5" operator="equal">
       <formula>FALSE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M21">
+  <conditionalFormatting sqref="O3:O22">
     <cfRule type="cellIs" dxfId="11" priority="4" operator="equal">
       <formula>FALSE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N21">
+  <conditionalFormatting sqref="P3:P22">
     <cfRule type="cellIs" dxfId="10" priority="3" operator="equal">
       <formula>FALSE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O21">
+  <conditionalFormatting sqref="Q3:Q22">
     <cfRule type="cellIs" dxfId="9" priority="2" operator="equal">
       <formula>FALSE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P21">
+  <conditionalFormatting sqref="R3:R22">
     <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
       <formula>FALSE</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="K14" r:id="rId1" display="mailto:john.smith@email.com"/>
-    <hyperlink ref="K7" r:id="rId2" display="mailto:sara.khan@email.com"/>
-    <hyperlink ref="K16" r:id="rId3" display="mailto:mike.j@email.com"/>
-    <hyperlink ref="K11" r:id="rId4" display="mailto:emily.d@email.com"/>
-    <hyperlink ref="K20" r:id="rId5" display="mailto:raj.patel@email.com"/>
-    <hyperlink ref="K4" r:id="rId6" display="mailto:anna.lee@email.com"/>
-    <hyperlink ref="K9" r:id="rId7" display="mailto:chris.b@email.com"/>
-    <hyperlink ref="K15" r:id="rId8" display="mailto:david.w@email.com"/>
-    <hyperlink ref="K2" r:id="rId9" display="mailto:lisa.t@email.com"/>
-    <hyperlink ref="K10" r:id="rId10" display="mailto:tom.a@email.com"/>
-    <hyperlink ref="K18" r:id="rId11" display="mailto:nina.g@email.com"/>
-    <hyperlink ref="K6" r:id="rId12" display="mailto:alex.m@email.com"/>
-    <hyperlink ref="K12" r:id="rId13" display="mailto:kevin.w@email.com"/>
-    <hyperlink ref="K21" r:id="rId14" display="mailto:priya.s@email.com"/>
-    <hyperlink ref="K3" r:id="rId15" display="mailto:daniel.c@email.com"/>
-    <hyperlink ref="K13" r:id="rId16" display="mailto:sophia.l@email.com"/>
-    <hyperlink ref="K17" r:id="rId17" display="mailto:james.w@email.com"/>
-    <hyperlink ref="K5" r:id="rId18" display="mailto:olivia.h@email.com"/>
-    <hyperlink ref="K8" r:id="rId19" display="mailto:ethan.a@email.com"/>
-    <hyperlink ref="K19" r:id="rId20" display="mailto:chloe.y@email.com"/>
+    <hyperlink ref="J15" r:id="rId1" display="mailto:john.smith@email.com"/>
+    <hyperlink ref="J8" r:id="rId2" display="mailto:sara.khan@email.com"/>
+    <hyperlink ref="J17" r:id="rId3" display="mailto:mike.j@email.com"/>
+    <hyperlink ref="J12" r:id="rId4" display="mailto:emily.d@email.com"/>
+    <hyperlink ref="J21" r:id="rId5" display="mailto:raj.patel@email.com"/>
+    <hyperlink ref="J5" r:id="rId6" display="mailto:anna.lee@email.com"/>
+    <hyperlink ref="J10" r:id="rId7" display="mailto:chris.b@email.com"/>
+    <hyperlink ref="J16" r:id="rId8" display="mailto:david.w@email.com"/>
+    <hyperlink ref="J3" r:id="rId9" display="mailto:lisa.t@email.com"/>
+    <hyperlink ref="J11" r:id="rId10" display="mailto:tom.a@email.com"/>
+    <hyperlink ref="J19" r:id="rId11" display="mailto:nina.g@email.com"/>
+    <hyperlink ref="J7" r:id="rId12" display="mailto:alex.m@email.com"/>
+    <hyperlink ref="J13" r:id="rId13" display="mailto:kevin.w@email.com"/>
+    <hyperlink ref="J22" r:id="rId14" display="mailto:priya.s@email.com"/>
+    <hyperlink ref="J4" r:id="rId15" display="mailto:daniel.c@email.com"/>
+    <hyperlink ref="J14" r:id="rId16" display="mailto:sophia.l@email.com"/>
+    <hyperlink ref="J18" r:id="rId17" display="mailto:james.w@email.com"/>
+    <hyperlink ref="J6" r:id="rId18" display="mailto:olivia.h@email.com"/>
+    <hyperlink ref="J9" r:id="rId19" display="mailto:ethan.a@email.com"/>
+    <hyperlink ref="J20" r:id="rId20" display="mailto:chloe.y@email.com"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId21"/>
@@ -2576,24 +2578,1808 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.109375" style="2" customWidth="1"/>
-    <col min="11" max="13" width="10.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.88671875" style="2"/>
+    <col min="3" max="3" width="13.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.77734375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="19" style="2" customWidth="1"/>
+    <col min="11" max="11" width="13.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="J1" s="48" t="s">
+        <v>131</v>
+      </c>
+      <c r="K1" s="48"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="46" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="46" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="46" t="s">
+        <v>112</v>
+      </c>
+      <c r="F2" s="46" t="s">
+        <v>113</v>
+      </c>
+      <c r="G2" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="46" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="46" t="s">
+        <v>76</v>
+      </c>
+      <c r="K2" s="46" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="5">
+        <v>46000</v>
+      </c>
+      <c r="F3" s="5">
+        <v>50000</v>
+      </c>
+      <c r="G3" s="5">
+        <v>2000</v>
+      </c>
+      <c r="H3" s="5">
+        <v>2</v>
+      </c>
+      <c r="J3" s="7" t="str">
+        <f>IF(E3&lt;F3,"Got Hike","No Hike")</f>
+        <v>Got Hike</v>
+      </c>
+      <c r="K3" s="47" t="str">
+        <f xml:space="preserve">
+IF(E3&lt;51000,"Low",
+IF(E3&lt;68000,"Avg","High"))</f>
+        <v>Low</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="5">
+        <v>45000</v>
+      </c>
+      <c r="F4" s="5">
+        <v>80000</v>
+      </c>
+      <c r="G4" s="5">
+        <v>2200</v>
+      </c>
+      <c r="H4" s="5">
+        <v>2</v>
+      </c>
+      <c r="J4" s="7" t="str">
+        <f>IF(E4&lt;F4,"Got Hike","No Hike")</f>
+        <v>Got Hike</v>
+      </c>
+      <c r="K4" s="47" t="str">
+        <f t="shared" ref="K4:K22" si="0" xml:space="preserve">
+IF(E4&lt;51000,"Low",
+IF(E4&lt;68000,"Avg","High"))</f>
+        <v>Low</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="5">
+        <v>47000</v>
+      </c>
+      <c r="F5" s="5">
+        <v>47000</v>
+      </c>
+      <c r="G5" s="5">
+        <v>2500</v>
+      </c>
+      <c r="H5" s="5">
+        <v>3</v>
+      </c>
+      <c r="J5" s="7" t="str">
+        <f t="shared" ref="J5:J22" si="1">IF(E5&lt;F5,"Got Hike","No Hike")</f>
+        <v>No Hike</v>
+      </c>
+      <c r="K5" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>Low</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="5">
+        <v>47000</v>
+      </c>
+      <c r="F6" s="5">
+        <v>47000</v>
+      </c>
+      <c r="G6" s="5">
+        <v>2600</v>
+      </c>
+      <c r="H6" s="5">
+        <v>3</v>
+      </c>
+      <c r="J6" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>No Hike</v>
+      </c>
+      <c r="K6" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>Low</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="5">
+        <v>49000</v>
+      </c>
+      <c r="F7" s="5">
+        <v>49000</v>
+      </c>
+      <c r="G7" s="5">
+        <v>2800</v>
+      </c>
+      <c r="H7" s="5">
+        <v>3</v>
+      </c>
+      <c r="J7" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>No Hike</v>
+      </c>
+      <c r="K7" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>Low</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="5">
+        <v>48000</v>
+      </c>
+      <c r="F8" s="5">
+        <f>48000+1000</f>
+        <v>49000</v>
+      </c>
+      <c r="G8" s="5">
+        <v>3000</v>
+      </c>
+      <c r="H8" s="5">
+        <v>3</v>
+      </c>
+      <c r="J8" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>Got Hike</v>
+      </c>
+      <c r="K8" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>Low</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="5">
+        <v>52000</v>
+      </c>
+      <c r="F9" s="5">
+        <v>52000</v>
+      </c>
+      <c r="G9" s="5">
+        <v>3900</v>
+      </c>
+      <c r="H9" s="5">
+        <v>4</v>
+      </c>
+      <c r="J9" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>No Hike</v>
+      </c>
+      <c r="K9" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>Avg</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="5">
+        <v>51000</v>
+      </c>
+      <c r="F10" s="5">
+        <v>20000</v>
+      </c>
+      <c r="G10" s="5">
+        <v>4000</v>
+      </c>
+      <c r="H10" s="5">
+        <v>4</v>
+      </c>
+      <c r="J10" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>No Hike</v>
+      </c>
+      <c r="K10" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>Avg</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="5">
+        <v>53000</v>
+      </c>
+      <c r="F11" s="5">
+        <v>53000</v>
+      </c>
+      <c r="G11" s="5">
+        <v>4200</v>
+      </c>
+      <c r="H11" s="5">
+        <v>4</v>
+      </c>
+      <c r="J11" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>No Hike</v>
+      </c>
+      <c r="K11" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>Avg</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" s="5">
+        <v>54000</v>
+      </c>
+      <c r="F12" s="5">
+        <v>54000</v>
+      </c>
+      <c r="G12" s="5">
+        <v>4500</v>
+      </c>
+      <c r="H12" s="5">
+        <v>4</v>
+      </c>
+      <c r="J12" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>No Hike</v>
+      </c>
+      <c r="K12" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>Avg</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="5">
+        <v>55000</v>
+      </c>
+      <c r="F13" s="5">
+        <f>55000-1000</f>
+        <v>54000</v>
+      </c>
+      <c r="G13" s="5">
+        <v>4700</v>
+      </c>
+      <c r="H13" s="5">
+        <v>4</v>
+      </c>
+      <c r="J13" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>No Hike</v>
+      </c>
+      <c r="K13" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>Avg</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" s="5">
+        <v>56000</v>
+      </c>
+      <c r="F14" s="5">
+        <v>56000</v>
+      </c>
+      <c r="G14" s="5">
+        <v>4800</v>
+      </c>
+      <c r="H14" s="5">
+        <v>4</v>
+      </c>
+      <c r="J14" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>No Hike</v>
+      </c>
+      <c r="K14" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>Avg</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" s="5">
+        <v>52000</v>
+      </c>
+      <c r="F15" s="5">
+        <v>52000</v>
+      </c>
+      <c r="G15" s="5">
+        <v>5000</v>
+      </c>
+      <c r="H15" s="5">
+        <v>4</v>
+      </c>
+      <c r="J15" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>No Hike</v>
+      </c>
+      <c r="K15" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>Avg</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="5">
+        <v>68000</v>
+      </c>
+      <c r="F16" s="5">
+        <v>68000</v>
+      </c>
+      <c r="G16" s="5">
+        <v>6000</v>
+      </c>
+      <c r="H16" s="5">
+        <v>5</v>
+      </c>
+      <c r="J16" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>No Hike</v>
+      </c>
+      <c r="K16" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>High</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E17" s="5">
+        <v>65000</v>
+      </c>
+      <c r="F17" s="5">
+        <v>65000</v>
+      </c>
+      <c r="G17" s="5">
+        <v>7000</v>
+      </c>
+      <c r="H17" s="5">
+        <v>5</v>
+      </c>
+      <c r="J17" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>No Hike</v>
+      </c>
+      <c r="K17" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>Avg</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" s="5">
+        <v>69000</v>
+      </c>
+      <c r="F18" s="5">
+        <v>69000</v>
+      </c>
+      <c r="G18" s="5">
+        <v>7100</v>
+      </c>
+      <c r="H18" s="5">
+        <v>5</v>
+      </c>
+      <c r="J18" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>No Hike</v>
+      </c>
+      <c r="K18" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>High</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E19" s="5">
+        <v>70000</v>
+      </c>
+      <c r="F19" s="5">
+        <v>70000</v>
+      </c>
+      <c r="G19" s="5">
+        <v>7500</v>
+      </c>
+      <c r="H19" s="5">
+        <v>5</v>
+      </c>
+      <c r="J19" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>No Hike</v>
+      </c>
+      <c r="K19" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>High</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E20" s="5">
+        <v>71000</v>
+      </c>
+      <c r="F20" s="5">
+        <v>71000</v>
+      </c>
+      <c r="G20" s="5">
+        <v>7800</v>
+      </c>
+      <c r="H20" s="5">
+        <v>5</v>
+      </c>
+      <c r="J20" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>No Hike</v>
+      </c>
+      <c r="K20" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>High</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21" s="5">
+        <v>72000</v>
+      </c>
+      <c r="F21" s="5">
+        <v>72000</v>
+      </c>
+      <c r="G21" s="5">
+        <v>8000</v>
+      </c>
+      <c r="H21" s="5">
+        <v>5</v>
+      </c>
+      <c r="J21" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>No Hike</v>
+      </c>
+      <c r="K21" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>High</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E22" s="5">
+        <v>73000</v>
+      </c>
+      <c r="F22" s="5">
+        <v>73000</v>
+      </c>
+      <c r="G22" s="5">
+        <v>8200</v>
+      </c>
+      <c r="H22" s="5">
+        <v>5</v>
+      </c>
+      <c r="J22" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>No Hike</v>
+      </c>
+      <c r="K22" s="47" t="str">
+        <f t="shared" si="0"/>
+        <v>High</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E23" s="2">
+        <f>SUM(E3:E22)</f>
+        <v>1143000</v>
+      </c>
+      <c r="F23" s="2">
+        <f>SUM(F3:F22)</f>
+        <v>1151000</v>
+      </c>
+      <c r="G23" s="2">
+        <f>SUM(G3:G22)</f>
+        <v>97800</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:K23"/>
+  <mergeCells count="1">
+    <mergeCell ref="J1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:T28"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.21875" style="28" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" style="28" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.6640625" style="28" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" style="28" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" style="28" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.88671875" style="28" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.88671875" style="28" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.109375" style="28" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13" style="28" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.21875" style="28" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.109375" style="28" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.109375" style="28" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.88671875" style="28"/>
+    <col min="15" max="15" width="10.21875" style="28" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.33203125" style="28" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7" style="28" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.44140625" style="28" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.21875" style="28" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.33203125" style="28" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7" style="28" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.109375" style="28" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="8.88671875" style="28"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="K1" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="L1" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="M1" s="40" t="s">
+        <v>127</v>
+      </c>
+      <c r="N1" s="40"/>
+      <c r="O1" s="40"/>
+      <c r="P1" s="40"/>
+      <c r="Q1" s="40"/>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="M2" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="N2" s="40"/>
+      <c r="O2" s="40"/>
+      <c r="P2" s="40"/>
+      <c r="Q2" s="40"/>
+    </row>
+    <row r="3" spans="1:20" ht="25.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="29" t="s">
+        <v>119</v>
+      </c>
+      <c r="F3" s="29" t="s">
+        <v>112</v>
+      </c>
+      <c r="G3" s="29" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="K3" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="L3" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="O3" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="S3" s="24" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="D4" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="32">
+        <v>1000</v>
+      </c>
+      <c r="F4" s="32">
+        <v>46000</v>
+      </c>
+      <c r="G4" s="32">
+        <v>2000</v>
+      </c>
+      <c r="H4" s="32">
+        <v>2</v>
+      </c>
+      <c r="I4" s="33">
+        <v>44668</v>
+      </c>
+      <c r="K4" s="28" t="str">
+        <f>IF(AND(E4&gt;5000,D4="South"),"Yes","No")</f>
+        <v>No</v>
+      </c>
+      <c r="L4" s="28" t="str">
+        <f>IF(OR(H4&gt;3,D4="North"),"Yes","No")</f>
+        <v>No</v>
+      </c>
+      <c r="O4" s="36" t="s">
+        <v>123</v>
+      </c>
+      <c r="P4" s="36" t="s">
+        <v>124</v>
+      </c>
+      <c r="S4" s="36" t="s">
+        <v>123</v>
+      </c>
+      <c r="T4" s="36" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="32">
+        <v>1500</v>
+      </c>
+      <c r="F5" s="32">
+        <v>45000</v>
+      </c>
+      <c r="G5" s="32">
+        <v>2200</v>
+      </c>
+      <c r="H5" s="32">
+        <v>2</v>
+      </c>
+      <c r="I5" s="33">
+        <v>44448</v>
+      </c>
+      <c r="K5" s="28" t="str">
+        <f t="shared" ref="K5:K23" si="0">IF(AND(E5&gt;5000,D5="South"),"Yes","No")</f>
+        <v>No</v>
+      </c>
+      <c r="L5" s="28" t="str">
+        <f t="shared" ref="L5:L23" si="1">IF(OR(H5&gt;3,D5="North"),"Yes","No")</f>
+        <v>No</v>
+      </c>
+      <c r="O5" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="P5" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="S5" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" s="36" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="32">
+        <v>2000</v>
+      </c>
+      <c r="F6" s="32">
+        <v>47000</v>
+      </c>
+      <c r="G6" s="32">
+        <v>2500</v>
+      </c>
+      <c r="H6" s="32">
+        <v>3</v>
+      </c>
+      <c r="I6" s="33">
+        <v>44359</v>
+      </c>
+      <c r="K6" s="28" t="str">
+        <f t="shared" si="0"/>
+        <v>No</v>
+      </c>
+      <c r="L6" s="28" t="str">
+        <f t="shared" si="1"/>
+        <v>Yes</v>
+      </c>
+      <c r="O6" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="S6" s="37" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" s="32" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" s="32" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="32">
+        <v>2500</v>
+      </c>
+      <c r="F7" s="32">
+        <v>47000</v>
+      </c>
+      <c r="G7" s="32">
+        <v>2600</v>
+      </c>
+      <c r="H7" s="32">
+        <v>3</v>
+      </c>
+      <c r="I7" s="33">
+        <v>44620</v>
+      </c>
+      <c r="K7" s="28" t="str">
+        <f t="shared" si="0"/>
+        <v>No</v>
+      </c>
+      <c r="L7" s="28" t="str">
+        <f t="shared" si="1"/>
+        <v>Yes</v>
+      </c>
+      <c r="O7" s="36"/>
+      <c r="S7" s="36"/>
+    </row>
+    <row r="8" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="32" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="D8" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="32">
+        <v>3000</v>
+      </c>
+      <c r="F8" s="32">
+        <v>49000</v>
+      </c>
+      <c r="G8" s="32">
+        <v>2800</v>
+      </c>
+      <c r="H8" s="32">
+        <v>3</v>
+      </c>
+      <c r="I8" s="33">
+        <v>44115</v>
+      </c>
+      <c r="K8" s="28" t="str">
+        <f t="shared" si="0"/>
+        <v>No</v>
+      </c>
+      <c r="L8" s="28" t="str">
+        <f t="shared" si="1"/>
+        <v>No</v>
+      </c>
+      <c r="O8" s="36" t="s">
+        <v>123</v>
+      </c>
+      <c r="P8" s="36" t="s">
+        <v>124</v>
+      </c>
+      <c r="S8" s="36" t="s">
+        <v>123</v>
+      </c>
+      <c r="T8" s="36" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="32">
+        <v>3500</v>
+      </c>
+      <c r="F9" s="32">
+        <v>48000</v>
+      </c>
+      <c r="G9" s="32">
+        <v>3000</v>
+      </c>
+      <c r="H9" s="32">
+        <v>3</v>
+      </c>
+      <c r="I9" s="33">
+        <v>44022</v>
+      </c>
+      <c r="K9" s="28" t="str">
+        <f t="shared" si="0"/>
+        <v>No</v>
+      </c>
+      <c r="L9" s="28" t="str">
+        <f t="shared" si="1"/>
+        <v>No</v>
+      </c>
+      <c r="O9" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="P9" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="S9" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" s="36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="32" t="s">
+        <v>70</v>
+      </c>
+      <c r="B10" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="D10" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="32">
+        <v>4000</v>
+      </c>
+      <c r="F10" s="32">
+        <v>52000</v>
+      </c>
+      <c r="G10" s="32">
+        <v>3900</v>
+      </c>
+      <c r="H10" s="32">
+        <v>4</v>
+      </c>
+      <c r="I10" s="33">
+        <v>44329</v>
+      </c>
+      <c r="K10" s="28" t="str">
+        <f t="shared" si="0"/>
+        <v>No</v>
+      </c>
+      <c r="L10" s="28" t="str">
+        <f t="shared" si="1"/>
+        <v>Yes</v>
+      </c>
+      <c r="O10" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="S10" s="37" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" s="32">
+        <v>4500</v>
+      </c>
+      <c r="F11" s="32">
+        <v>51000</v>
+      </c>
+      <c r="G11" s="32">
+        <v>4000</v>
+      </c>
+      <c r="H11" s="32">
+        <v>4</v>
+      </c>
+      <c r="I11" s="33">
+        <v>43886</v>
+      </c>
+      <c r="K11" s="28" t="str">
+        <f t="shared" si="0"/>
+        <v>No</v>
+      </c>
+      <c r="L11" s="28" t="str">
+        <f t="shared" si="1"/>
+        <v>Yes</v>
+      </c>
+      <c r="O11" s="36"/>
+      <c r="S11" s="36"/>
+    </row>
+    <row r="12" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="32" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="32">
+        <v>5000</v>
+      </c>
+      <c r="F12" s="32">
+        <v>53000</v>
+      </c>
+      <c r="G12" s="32">
+        <v>4200</v>
+      </c>
+      <c r="H12" s="32">
+        <v>4</v>
+      </c>
+      <c r="I12" s="33">
+        <v>44531</v>
+      </c>
+      <c r="K12" s="28" t="str">
+        <f t="shared" si="0"/>
+        <v>No</v>
+      </c>
+      <c r="L12" s="28" t="str">
+        <f t="shared" si="1"/>
+        <v>Yes</v>
+      </c>
+      <c r="O12" s="36" t="s">
+        <v>123</v>
+      </c>
+      <c r="P12" s="36" t="s">
+        <v>124</v>
+      </c>
+      <c r="S12" s="36" t="s">
+        <v>123</v>
+      </c>
+      <c r="T12" s="36" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="34" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" s="34">
+        <v>5500</v>
+      </c>
+      <c r="F13" s="34">
+        <v>54000</v>
+      </c>
+      <c r="G13" s="34">
+        <v>4500</v>
+      </c>
+      <c r="H13" s="34">
+        <v>4</v>
+      </c>
+      <c r="I13" s="35">
+        <v>44566</v>
+      </c>
+      <c r="K13" s="28" t="str">
+        <f t="shared" si="0"/>
+        <v>Yes</v>
+      </c>
+      <c r="L13" s="28" t="str">
+        <f t="shared" si="1"/>
+        <v>Yes</v>
+      </c>
+      <c r="O13" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="P13" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="S13" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" s="36" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="34" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="34">
+        <v>6000</v>
+      </c>
+      <c r="F14" s="34">
+        <v>55000</v>
+      </c>
+      <c r="G14" s="34">
+        <v>4700</v>
+      </c>
+      <c r="H14" s="34">
+        <v>4</v>
+      </c>
+      <c r="I14" s="35">
+        <v>43527</v>
+      </c>
+      <c r="K14" s="28" t="str">
+        <f t="shared" si="0"/>
+        <v>No</v>
+      </c>
+      <c r="L14" s="28" t="str">
+        <f t="shared" si="1"/>
+        <v>Yes</v>
+      </c>
+      <c r="O14" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="S14" s="37" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" ht="25.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="B15" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="C15" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="D15" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="34">
+        <v>6500</v>
+      </c>
+      <c r="F15" s="34">
+        <v>56000</v>
+      </c>
+      <c r="G15" s="34">
+        <v>4800</v>
+      </c>
+      <c r="H15" s="34">
+        <v>4</v>
+      </c>
+      <c r="I15" s="35">
+        <v>43849</v>
+      </c>
+      <c r="K15" s="28" t="str">
+        <f t="shared" si="0"/>
+        <v>Yes</v>
+      </c>
+      <c r="L15" s="28" t="str">
+        <f t="shared" si="1"/>
+        <v>Yes</v>
+      </c>
+      <c r="O15" s="36"/>
+      <c r="S15" s="24"/>
+    </row>
+    <row r="16" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" s="34">
+        <v>7000</v>
+      </c>
+      <c r="F16" s="34">
+        <v>52000</v>
+      </c>
+      <c r="G16" s="34">
+        <v>5000</v>
+      </c>
+      <c r="H16" s="34">
+        <v>4</v>
+      </c>
+      <c r="I16" s="35">
+        <v>44270</v>
+      </c>
+      <c r="K16" s="28" t="str">
+        <f t="shared" si="0"/>
+        <v>No</v>
+      </c>
+      <c r="L16" s="28" t="str">
+        <f t="shared" si="1"/>
+        <v>Yes</v>
+      </c>
+      <c r="O16" s="36" t="s">
+        <v>123</v>
+      </c>
+      <c r="P16" s="36" t="s">
+        <v>124</v>
+      </c>
+      <c r="S16" s="36" t="s">
+        <v>123</v>
+      </c>
+      <c r="T16" s="36" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="34" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="34" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="34" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" s="34">
+        <v>7500</v>
+      </c>
+      <c r="F17" s="34">
+        <v>68000</v>
+      </c>
+      <c r="G17" s="34">
+        <v>6000</v>
+      </c>
+      <c r="H17" s="34">
+        <v>5</v>
+      </c>
+      <c r="I17" s="35">
+        <v>43707</v>
+      </c>
+      <c r="K17" s="28" t="str">
+        <f t="shared" si="0"/>
+        <v>Yes</v>
+      </c>
+      <c r="L17" s="28" t="str">
+        <f t="shared" si="1"/>
+        <v>Yes</v>
+      </c>
+      <c r="O17" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="P17" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="S17" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" s="36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="34" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" s="34">
+        <v>8000</v>
+      </c>
+      <c r="F18" s="34">
+        <v>65000</v>
+      </c>
+      <c r="G18" s="34">
+        <v>7000</v>
+      </c>
+      <c r="H18" s="34">
+        <v>5</v>
+      </c>
+      <c r="I18" s="35">
+        <v>43791</v>
+      </c>
+      <c r="K18" s="28" t="str">
+        <f t="shared" si="0"/>
+        <v>No</v>
+      </c>
+      <c r="L18" s="28" t="str">
+        <f t="shared" si="1"/>
+        <v>Yes</v>
+      </c>
+      <c r="O18" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="S18" s="38" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A19" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" s="34" t="s">
+        <v>65</v>
+      </c>
+      <c r="C19" s="34" t="s">
+        <v>65</v>
+      </c>
+      <c r="D19" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" s="34">
+        <v>8500</v>
+      </c>
+      <c r="F19" s="34">
+        <v>69000</v>
+      </c>
+      <c r="G19" s="34">
+        <v>7100</v>
+      </c>
+      <c r="H19" s="34">
+        <v>5</v>
+      </c>
+      <c r="I19" s="35">
+        <v>43622</v>
+      </c>
+      <c r="K19" s="28" t="str">
+        <f t="shared" si="0"/>
+        <v>No</v>
+      </c>
+      <c r="L19" s="28" t="str">
+        <f t="shared" si="1"/>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A20" s="34" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" s="34" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" s="34" t="s">
+        <v>47</v>
+      </c>
+      <c r="D20" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" s="34">
+        <v>9000</v>
+      </c>
+      <c r="F20" s="34">
+        <v>70000</v>
+      </c>
+      <c r="G20" s="34">
+        <v>7500</v>
+      </c>
+      <c r="H20" s="34">
+        <v>5</v>
+      </c>
+      <c r="I20" s="35">
+        <v>43241</v>
+      </c>
+      <c r="K20" s="28" t="str">
+        <f t="shared" si="0"/>
+        <v>No</v>
+      </c>
+      <c r="L20" s="28" t="str">
+        <f t="shared" si="1"/>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A21" s="34" t="s">
+        <v>73</v>
+      </c>
+      <c r="B21" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="D21" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="E21" s="34">
+        <v>9500</v>
+      </c>
+      <c r="F21" s="34">
+        <v>71000</v>
+      </c>
+      <c r="G21" s="34">
+        <v>7800</v>
+      </c>
+      <c r="H21" s="34">
+        <v>5</v>
+      </c>
+      <c r="I21" s="35">
+        <v>43458</v>
+      </c>
+      <c r="K21" s="28" t="str">
+        <f t="shared" si="0"/>
+        <v>Yes</v>
+      </c>
+      <c r="L21" s="28" t="str">
+        <f t="shared" si="1"/>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A22" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="34" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="34" t="s">
+        <v>29</v>
+      </c>
+      <c r="D22" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22" s="34">
+        <v>10000</v>
+      </c>
+      <c r="F22" s="34">
+        <v>72000</v>
+      </c>
+      <c r="G22" s="34">
+        <v>8000</v>
+      </c>
+      <c r="H22" s="34">
+        <v>5</v>
+      </c>
+      <c r="I22" s="35">
+        <v>43361</v>
+      </c>
+      <c r="K22" s="28" t="str">
+        <f t="shared" si="0"/>
+        <v>No</v>
+      </c>
+      <c r="L22" s="28" t="str">
+        <f t="shared" si="1"/>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A23" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="B23" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="C23" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="D23" s="34" t="s">
+        <v>22</v>
+      </c>
+      <c r="E23" s="34">
+        <v>10500</v>
+      </c>
+      <c r="F23" s="34">
+        <v>73000</v>
+      </c>
+      <c r="G23" s="34">
+        <v>8200</v>
+      </c>
+      <c r="H23" s="34">
+        <v>5</v>
+      </c>
+      <c r="I23" s="35">
+        <v>42930</v>
+      </c>
+      <c r="K23" s="28" t="str">
+        <f t="shared" si="0"/>
+        <v>No</v>
+      </c>
+      <c r="L23" s="28" t="str">
+        <f t="shared" si="1"/>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="F24" s="28">
+        <f>SUM(F4:F23)</f>
+        <v>1143000</v>
+      </c>
+      <c r="G24" s="28">
+        <f>SUM(G4:G23)</f>
+        <v>97800</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="I26" s="28" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="I27" s="28" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="I28" s="28" t="s">
+        <v>118</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:L24"/>
+  <mergeCells count="2">
+    <mergeCell ref="M1:Q1"/>
+    <mergeCell ref="M2:Q2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="K4:K23">
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L3:L23">
+    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:W21"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.88671875" customWidth="1"/>
+    <col min="8" max="8" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2601,47 +4387,62 @@
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>4</v>
-      </c>
       <c r="F1" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+      <c r="G1" s="41"/>
+      <c r="H1" s="44" t="s">
+        <v>130</v>
+      </c>
+      <c r="I1" s="44" t="s">
+        <v>129</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="S1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="T1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="U1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="V1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="W1" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>40</v>
       </c>
@@ -2649,53 +4450,64 @@
         <v>41</v>
       </c>
       <c r="C2" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="5">
+      <c r="F2" s="5">
         <v>46000</v>
       </c>
-      <c r="F2" s="5">
-        <v>2000</v>
-      </c>
-      <c r="G2" s="5">
-        <v>2</v>
-      </c>
-      <c r="H2" s="6">
-        <v>44668</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="J2" s="3"/>
-      <c r="K2" s="2" t="b">
-        <f>G2&gt;2</f>
-        <v>0</v>
-      </c>
-      <c r="L2" s="2" t="str">
-        <f t="shared" ref="L2" si="0">IF(F2&lt;4000,"Low","Good")</f>
-        <v>Low</v>
-      </c>
-      <c r="M2" s="2" t="str">
-        <f>IF(F2&lt;4000,"Low",IF(F2&lt;6000,"Avg","Good"))</f>
-        <v>Low</v>
-      </c>
-      <c r="N2" s="2" t="str">
-        <f>IF(AND(C2="HR",D2="West"),"Yes","No")</f>
-        <v>No</v>
-      </c>
-      <c r="O2" s="2" t="str">
-        <f>IF(OR(C2="IT",D2="South"),"Yes","No")</f>
-        <v>No</v>
-      </c>
-      <c r="P2" s="2" t="b">
-        <f>NOT(F2&lt;5000)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="G2" s="42"/>
+      <c r="H2" s="45" t="str">
+        <f>IFERROR(VLOOKUP(A2,$K$1:$P$16,1,FALSE),"Not Found")</f>
+        <v>E009</v>
+      </c>
+      <c r="I2" s="45" t="str">
+        <f>IFERROR(VLOOKUP(A2,$K$1:$P$16,1,FALSE),VLOOKUP(A2,$R$1:$W$6,1,FALSE))</f>
+        <v>E009</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P2" s="5">
+        <v>46000</v>
+      </c>
+      <c r="R2" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="S2" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="T2" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="U2" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="V2" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="W2" s="22">
+        <v>69000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>58</v>
       </c>
@@ -2703,53 +4515,64 @@
         <v>59</v>
       </c>
       <c r="C3" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="E3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="5">
+      <c r="F3" s="5">
         <v>45000</v>
       </c>
-      <c r="F3" s="5">
-        <v>2200</v>
-      </c>
-      <c r="G3" s="5">
-        <v>2</v>
-      </c>
-      <c r="H3" s="6">
-        <v>44448</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="J3" s="3"/>
-      <c r="K3" s="2" t="b">
-        <f t="shared" ref="K3:K21" si="1">G3&gt;2</f>
-        <v>0</v>
-      </c>
-      <c r="L3" s="2" t="str">
-        <f>IF(F3&lt;4000,"Low","Good")</f>
-        <v>Low</v>
-      </c>
-      <c r="M3" s="2" t="str">
-        <f t="shared" ref="M3:M21" si="2">IF(F3&lt;4000,"Low",IF(F3&lt;6000,"Avg","Good"))</f>
-        <v>Low</v>
-      </c>
-      <c r="N3" s="2" t="str">
-        <f t="shared" ref="N3:N21" si="3">IF(AND(C3="HR",D3="West"),"Yes","No")</f>
-        <v>Yes</v>
-      </c>
-      <c r="O3" s="2" t="str">
-        <f t="shared" ref="O3:O21" si="4">IF(OR(C3="IT",D3="South"),"Yes","No")</f>
-        <v>No</v>
-      </c>
-      <c r="P3" s="2" t="b">
-        <f t="shared" ref="P3:P21" si="5">NOT(F3&lt;5000)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="G3" s="42"/>
+      <c r="H3" s="45" t="str">
+        <f t="shared" ref="H3:H21" si="0">IFERROR(VLOOKUP(A3,$K$1:$P$16,1,FALSE),"Not Found")</f>
+        <v>E015</v>
+      </c>
+      <c r="I3" s="45" t="str">
+        <f t="shared" ref="I3:I21" si="1">IFERROR(VLOOKUP(A3,$K$1:$P$16,1,FALSE),VLOOKUP(A3,$R$1:$W$6,1,FALSE))</f>
+        <v>E015</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="P3" s="5">
+        <v>45000</v>
+      </c>
+      <c r="R3" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="S3" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="T3" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="U3" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="V3" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="W3" s="22">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>31</v>
       </c>
@@ -2757,53 +4580,64 @@
         <v>32</v>
       </c>
       <c r="C4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="5">
+      <c r="F4" s="5">
         <v>47000</v>
       </c>
-      <c r="F4" s="5">
-        <v>2500</v>
-      </c>
-      <c r="G4" s="5">
-        <v>3</v>
-      </c>
-      <c r="H4" s="6">
-        <v>44359</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="J4" s="3"/>
-      <c r="K4" s="2" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="L4" s="2" t="str">
-        <f t="shared" ref="L4:L21" si="6">IF(F4&lt;4000,"Low","Good")</f>
-        <v>Low</v>
-      </c>
-      <c r="M4" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Low</v>
-      </c>
-      <c r="N4" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>No</v>
-      </c>
-      <c r="O4" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>No</v>
-      </c>
-      <c r="P4" s="2" t="b">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="G4" s="42"/>
+      <c r="H4" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>E006</v>
+      </c>
+      <c r="I4" s="45" t="str">
+        <f t="shared" si="1"/>
+        <v>E006</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="N4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="O4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="P4" s="5">
+        <v>47000</v>
+      </c>
+      <c r="R4" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="S4" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="T4" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="U4" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="V4" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="W4" s="22">
+        <v>71000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>67</v>
       </c>
@@ -2811,53 +4645,64 @@
         <v>68</v>
       </c>
       <c r="C5" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="E5" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="5">
+      <c r="F5" s="5">
         <v>47000</v>
       </c>
-      <c r="F5" s="5">
-        <v>2600</v>
-      </c>
-      <c r="G5" s="5">
-        <v>3</v>
-      </c>
-      <c r="H5" s="6">
-        <v>44620</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="J5" s="3"/>
-      <c r="K5" s="2" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="L5" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>Low</v>
-      </c>
-      <c r="M5" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Low</v>
-      </c>
-      <c r="N5" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>No</v>
-      </c>
-      <c r="O5" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>No</v>
-      </c>
-      <c r="P5" s="2" t="b">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="G5" s="42"/>
+      <c r="H5" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>E018</v>
+      </c>
+      <c r="I5" s="45" t="str">
+        <f t="shared" si="1"/>
+        <v>E018</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="O5" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="P5" s="5">
+        <v>47000</v>
+      </c>
+      <c r="R5" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="S5" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="T5" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="U5" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="V5" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="W5" s="22">
+        <v>72000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>49</v>
       </c>
@@ -2865,53 +4710,64 @@
         <v>50</v>
       </c>
       <c r="C6" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="E6" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="5">
+      <c r="F6" s="5">
         <v>49000</v>
       </c>
-      <c r="F6" s="5">
-        <v>2800</v>
-      </c>
-      <c r="G6" s="5">
-        <v>3</v>
-      </c>
-      <c r="H6" s="6">
-        <v>44115</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="J6" s="3"/>
-      <c r="K6" s="2" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="L6" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>Low</v>
-      </c>
-      <c r="M6" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Low</v>
-      </c>
-      <c r="N6" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>No</v>
-      </c>
-      <c r="O6" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>Yes</v>
-      </c>
-      <c r="P6" s="2" t="b">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="G6" s="42"/>
+      <c r="H6" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>E012</v>
+      </c>
+      <c r="I6" s="45" t="str">
+        <f t="shared" si="1"/>
+        <v>E012</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="M6" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="N6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="O6" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="P6" s="5">
+        <v>49000</v>
+      </c>
+      <c r="R6" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="S6" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="T6" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="U6" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="V6" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="W6" s="22">
+        <v>73000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>14</v>
       </c>
@@ -2919,53 +4775,46 @@
         <v>15</v>
       </c>
       <c r="C7" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="E7" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="5">
+      <c r="F7" s="5">
         <v>48000</v>
       </c>
-      <c r="F7" s="5">
-        <v>3000</v>
-      </c>
-      <c r="G7" s="5">
-        <v>3</v>
-      </c>
-      <c r="H7" s="6">
-        <v>44022</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="J7" s="3"/>
-      <c r="K7" s="2" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="L7" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>Low</v>
-      </c>
-      <c r="M7" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Low</v>
-      </c>
-      <c r="N7" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>Yes</v>
-      </c>
-      <c r="O7" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>No</v>
-      </c>
-      <c r="P7" s="2" t="b">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="G7" s="42"/>
+      <c r="H7" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>E002</v>
+      </c>
+      <c r="I7" s="45" t="str">
+        <f t="shared" si="1"/>
+        <v>E002</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="M7" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="N7" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="O7" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="P7" s="5">
+        <v>48000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>70</v>
       </c>
@@ -2973,53 +4822,46 @@
         <v>71</v>
       </c>
       <c r="C8" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="E8" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="5">
+      <c r="F8" s="5">
         <v>52000</v>
       </c>
-      <c r="F8" s="5">
-        <v>3900</v>
-      </c>
-      <c r="G8" s="5">
-        <v>4</v>
-      </c>
-      <c r="H8" s="6">
-        <v>44329</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="J8" s="3"/>
-      <c r="K8" s="2" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="L8" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>Low</v>
-      </c>
-      <c r="M8" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Low</v>
-      </c>
-      <c r="N8" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>No</v>
-      </c>
-      <c r="O8" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>No</v>
-      </c>
-      <c r="P8" s="2" t="b">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="G8" s="42"/>
+      <c r="H8" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>E019</v>
+      </c>
+      <c r="I8" s="45" t="str">
+        <f t="shared" si="1"/>
+        <v>E019</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="M8" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="N8" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="O8" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="P8" s="5">
+        <v>52000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>34</v>
       </c>
@@ -3027,53 +4869,46 @@
         <v>35</v>
       </c>
       <c r="C9" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="E9" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="5">
+      <c r="F9" s="5">
         <v>51000</v>
       </c>
-      <c r="F9" s="5">
-        <v>4000</v>
-      </c>
-      <c r="G9" s="5">
-        <v>4</v>
-      </c>
-      <c r="H9" s="6">
-        <v>43886</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="J9" s="3"/>
-      <c r="K9" s="2" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="L9" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>Good</v>
-      </c>
-      <c r="M9" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Avg</v>
-      </c>
-      <c r="N9" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>No</v>
-      </c>
-      <c r="O9" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>No</v>
-      </c>
-      <c r="P9" s="2" t="b">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="G9" s="42"/>
+      <c r="H9" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>E007</v>
+      </c>
+      <c r="I9" s="45" t="str">
+        <f t="shared" si="1"/>
+        <v>E007</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="M9" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="N9" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="O9" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="P9" s="5">
+        <v>51000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>43</v>
       </c>
@@ -3081,53 +4916,46 @@
         <v>44</v>
       </c>
       <c r="C10" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="E10" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E10" s="5">
+      <c r="F10" s="5">
         <v>53000</v>
       </c>
-      <c r="F10" s="5">
-        <v>4200</v>
-      </c>
-      <c r="G10" s="5">
-        <v>4</v>
-      </c>
-      <c r="H10" s="6">
-        <v>44531</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="J10" s="3"/>
-      <c r="K10" s="2" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="L10" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>Good</v>
-      </c>
-      <c r="M10" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Avg</v>
-      </c>
-      <c r="N10" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>No</v>
-      </c>
-      <c r="O10" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>No</v>
-      </c>
-      <c r="P10" s="2" t="b">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="G10" s="42"/>
+      <c r="H10" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>E010</v>
+      </c>
+      <c r="I10" s="45" t="str">
+        <f t="shared" si="1"/>
+        <v>E010</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="M10" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="N10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="O10" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="P10" s="5">
+        <v>53000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>24</v>
       </c>
@@ -3135,53 +4963,46 @@
         <v>25</v>
       </c>
       <c r="C11" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="E11" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E11" s="5">
+      <c r="F11" s="5">
         <v>54000</v>
       </c>
-      <c r="F11" s="5">
-        <v>4500</v>
-      </c>
-      <c r="G11" s="5">
-        <v>4</v>
-      </c>
-      <c r="H11" s="6">
-        <v>44566</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="J11" s="3"/>
-      <c r="K11" s="2" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="L11" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>Good</v>
-      </c>
-      <c r="M11" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Avg</v>
-      </c>
-      <c r="N11" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>No</v>
-      </c>
-      <c r="O11" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>Yes</v>
-      </c>
-      <c r="P11" s="2" t="b">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="G11" s="42"/>
+      <c r="H11" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>E004</v>
+      </c>
+      <c r="I11" s="45" t="str">
+        <f t="shared" si="1"/>
+        <v>E004</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M11" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N11" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="O11" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="P11" s="5">
+        <v>54000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>52</v>
       </c>
@@ -3189,53 +5010,46 @@
         <v>53</v>
       </c>
       <c r="C12" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="E12" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E12" s="5">
+      <c r="F12" s="5">
         <v>55000</v>
       </c>
-      <c r="F12" s="5">
-        <v>4700</v>
-      </c>
-      <c r="G12" s="5">
-        <v>4</v>
-      </c>
-      <c r="H12" s="6">
-        <v>43527</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="J12" s="3"/>
-      <c r="K12" s="2" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="L12" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>Good</v>
-      </c>
-      <c r="M12" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Avg</v>
-      </c>
-      <c r="N12" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>No</v>
-      </c>
-      <c r="O12" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>No</v>
-      </c>
-      <c r="P12" s="2" t="b">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="G12" s="42"/>
+      <c r="H12" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>E013</v>
+      </c>
+      <c r="I12" s="45" t="str">
+        <f t="shared" si="1"/>
+        <v>E013</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="L12" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="M12" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="N12" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="O12" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P12" s="5">
+        <v>55000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>61</v>
       </c>
@@ -3243,53 +5057,46 @@
         <v>62</v>
       </c>
       <c r="C13" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D13" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="E13" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E13" s="5">
+      <c r="F13" s="5">
         <v>56000</v>
       </c>
-      <c r="F13" s="5">
-        <v>4800</v>
-      </c>
-      <c r="G13" s="5">
-        <v>4</v>
-      </c>
-      <c r="H13" s="6">
-        <v>43849</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="J13" s="3"/>
-      <c r="K13" s="2" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="L13" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>Good</v>
-      </c>
-      <c r="M13" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Avg</v>
-      </c>
-      <c r="N13" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>No</v>
-      </c>
-      <c r="O13" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>Yes</v>
-      </c>
-      <c r="P13" s="2" t="b">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="G13" s="42"/>
+      <c r="H13" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>E016</v>
+      </c>
+      <c r="I13" s="45" t="str">
+        <f t="shared" si="1"/>
+        <v>E016</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="M13" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="N13" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="O13" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="P13" s="5">
+        <v>56000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>9</v>
       </c>
@@ -3297,53 +5104,46 @@
         <v>10</v>
       </c>
       <c r="C14" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="E14" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E14" s="5">
+      <c r="F14" s="5">
         <v>52000</v>
       </c>
-      <c r="F14" s="5">
-        <v>5000</v>
-      </c>
-      <c r="G14" s="5">
-        <v>4</v>
-      </c>
-      <c r="H14" s="6">
-        <v>44270</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="J14" s="3"/>
-      <c r="K14" s="2" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="L14" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>Good</v>
-      </c>
-      <c r="M14" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Avg</v>
-      </c>
-      <c r="N14" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>No</v>
-      </c>
-      <c r="O14" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>No</v>
-      </c>
-      <c r="P14" s="2" t="b">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="G14" s="42"/>
+      <c r="H14" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>E001</v>
+      </c>
+      <c r="I14" s="45" t="str">
+        <f t="shared" si="1"/>
+        <v>E001</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="M14" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="N14" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="O14" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P14" s="5">
+        <v>52000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>37</v>
       </c>
@@ -3351,53 +5151,46 @@
         <v>38</v>
       </c>
       <c r="C15" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="E15" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E15" s="5">
+      <c r="F15" s="5">
         <v>68000</v>
       </c>
-      <c r="F15" s="5">
-        <v>6000</v>
-      </c>
-      <c r="G15" s="5">
-        <v>5</v>
-      </c>
-      <c r="H15" s="6">
-        <v>43707</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="J15" s="3"/>
-      <c r="K15" s="2" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="L15" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>Good</v>
-      </c>
-      <c r="M15" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Good</v>
-      </c>
-      <c r="N15" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>No</v>
-      </c>
-      <c r="O15" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>Yes</v>
-      </c>
-      <c r="P15" s="2" t="b">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="G15" s="42"/>
+      <c r="H15" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>E008</v>
+      </c>
+      <c r="I15" s="45" t="str">
+        <f t="shared" si="1"/>
+        <v>E008</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="M15" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="N15" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="O15" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="P15" s="5">
+        <v>68000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>19</v>
       </c>
@@ -3405,371 +5198,196 @@
         <v>20</v>
       </c>
       <c r="C16" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="E16" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E16" s="5">
+      <c r="F16" s="5">
         <v>65000</v>
       </c>
-      <c r="F16" s="5">
-        <v>7000</v>
-      </c>
-      <c r="G16" s="5">
-        <v>5</v>
-      </c>
-      <c r="H16" s="6">
-        <v>43791</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J16" s="3"/>
-      <c r="K16" s="2" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="L16" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>Good</v>
-      </c>
-      <c r="M16" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Good</v>
-      </c>
-      <c r="N16" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>No</v>
-      </c>
-      <c r="O16" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>Yes</v>
-      </c>
-      <c r="P16" s="2" t="b">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A17" s="5" t="s">
+      <c r="G16" s="42"/>
+      <c r="H16" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>E003</v>
+      </c>
+      <c r="I16" s="45" t="str">
+        <f t="shared" si="1"/>
+        <v>E003</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="L16" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="M16" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="N16" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="O16" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="P16" s="5">
+        <v>65000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="D17" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="E17" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E17" s="5">
+      <c r="F17" s="22">
         <v>69000</v>
       </c>
-      <c r="F17" s="5">
-        <v>7100</v>
-      </c>
-      <c r="G17" s="5">
-        <v>5</v>
-      </c>
-      <c r="H17" s="6">
-        <v>43622</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="J17" s="3"/>
-      <c r="K17" s="2" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="L17" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>Good</v>
-      </c>
-      <c r="M17" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Good</v>
-      </c>
-      <c r="N17" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>No</v>
-      </c>
-      <c r="O17" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>Yes</v>
-      </c>
-      <c r="P17" s="2" t="b">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A18" s="5" t="s">
+      <c r="G17" s="43"/>
+      <c r="H17" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Found</v>
+      </c>
+      <c r="I17" s="45" t="str">
+        <f>IFERROR(VLOOKUP(A17,$K$1:$P$16,1,FALSE),VLOOKUP(A17,$R$1:$W$6,1,FALSE))</f>
+        <v>E017</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="D18" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="E18" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="E18" s="5">
+      <c r="F18" s="22">
         <v>70000</v>
       </c>
-      <c r="F18" s="5">
-        <v>7500</v>
-      </c>
-      <c r="G18" s="5">
-        <v>5</v>
-      </c>
-      <c r="H18" s="6">
-        <v>43241</v>
-      </c>
-      <c r="I18" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="J18" s="3"/>
-      <c r="K18" s="2" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="L18" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>Good</v>
-      </c>
-      <c r="M18" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Good</v>
-      </c>
-      <c r="N18" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>No</v>
-      </c>
-      <c r="O18" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>Yes</v>
-      </c>
-      <c r="P18" s="2" t="b">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A19" s="5" t="s">
+      <c r="G18" s="43"/>
+      <c r="H18" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Found</v>
+      </c>
+      <c r="I18" s="45" t="str">
+        <f t="shared" si="1"/>
+        <v>E011</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="D19" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="E19" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="E19" s="5">
+      <c r="F19" s="22">
         <v>71000</v>
       </c>
-      <c r="F19" s="5">
-        <v>7800</v>
-      </c>
-      <c r="G19" s="5">
-        <v>5</v>
-      </c>
-      <c r="H19" s="6">
-        <v>43458</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="J19" s="3"/>
-      <c r="K19" s="2" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="L19" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>Good</v>
-      </c>
-      <c r="M19" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Good</v>
-      </c>
-      <c r="N19" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>No</v>
-      </c>
-      <c r="O19" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>Yes</v>
-      </c>
-      <c r="P19" s="2" t="b">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A20" s="5" t="s">
+      <c r="G19" s="43"/>
+      <c r="H19" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Found</v>
+      </c>
+      <c r="I19" s="45" t="str">
+        <f t="shared" si="1"/>
+        <v>E020</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="D20" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="E20" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E20" s="5">
+      <c r="F20" s="22">
         <v>72000</v>
       </c>
-      <c r="F20" s="5">
-        <v>8000</v>
-      </c>
-      <c r="G20" s="5">
-        <v>5</v>
-      </c>
-      <c r="H20" s="6">
-        <v>43361</v>
-      </c>
-      <c r="I20" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="J20" s="3"/>
-      <c r="K20" s="2" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="L20" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>Good</v>
-      </c>
-      <c r="M20" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Good</v>
-      </c>
-      <c r="N20" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>No</v>
-      </c>
-      <c r="O20" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>Yes</v>
-      </c>
-      <c r="P20" s="2" t="b">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A21" s="5" t="s">
+      <c r="G20" s="43"/>
+      <c r="H20" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Found</v>
+      </c>
+      <c r="I20" s="45" t="str">
+        <f t="shared" si="1"/>
+        <v>E005</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="D21" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="E21" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="E21" s="5">
+      <c r="F21" s="22">
         <v>73000</v>
       </c>
-      <c r="F21" s="5">
-        <v>8200</v>
-      </c>
-      <c r="G21" s="5">
-        <v>5</v>
-      </c>
-      <c r="H21" s="6">
-        <v>42930</v>
-      </c>
-      <c r="I21" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="J21" s="3"/>
-      <c r="K21" s="2" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="L21" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>Good</v>
-      </c>
-      <c r="M21" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>Good</v>
-      </c>
-      <c r="N21" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>No</v>
-      </c>
-      <c r="O21" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>Yes</v>
-      </c>
-      <c r="P21" s="2" t="b">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="E22" s="2">
-        <f>SUM(E2:E21)</f>
-        <v>1143000</v>
-      </c>
-      <c r="F22" s="2">
-        <f>SUM(F2:F21)</f>
-        <v>97800</v>
+      <c r="G21" s="43"/>
+      <c r="H21" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Found</v>
+      </c>
+      <c r="I21" s="45" t="str">
+        <f t="shared" si="1"/>
+        <v>E014</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:I21">
-    <sortCondition ref="F2:F21"/>
-  </sortState>
-  <conditionalFormatting sqref="K1:K21">
-    <cfRule type="containsText" dxfId="7" priority="1" operator="containsText" text="TRUE">
-      <formula>NOT(ISERROR(SEARCH("TRUE",K1)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="2" operator="containsText" text="FALSE">
-      <formula>NOT(ISERROR(SEARCH("FALSE",K1)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <hyperlinks>
-    <hyperlink ref="I14" r:id="rId1" display="mailto:john.smith@email.com"/>
-    <hyperlink ref="I7" r:id="rId2" display="mailto:sara.khan@email.com"/>
-    <hyperlink ref="I16" r:id="rId3" display="mailto:mike.j@email.com"/>
-    <hyperlink ref="I11" r:id="rId4" display="mailto:emily.d@email.com"/>
-    <hyperlink ref="I20" r:id="rId5" display="mailto:raj.patel@email.com"/>
-    <hyperlink ref="I4" r:id="rId6" display="mailto:anna.lee@email.com"/>
-    <hyperlink ref="I9" r:id="rId7" display="mailto:chris.b@email.com"/>
-    <hyperlink ref="I15" r:id="rId8" display="mailto:david.w@email.com"/>
-    <hyperlink ref="I2" r:id="rId9" display="mailto:lisa.t@email.com"/>
-    <hyperlink ref="I10" r:id="rId10" display="mailto:tom.a@email.com"/>
-    <hyperlink ref="I18" r:id="rId11" display="mailto:nina.g@email.com"/>
-    <hyperlink ref="I6" r:id="rId12" display="mailto:alex.m@email.com"/>
-    <hyperlink ref="I12" r:id="rId13" display="mailto:kevin.w@email.com"/>
-    <hyperlink ref="I21" r:id="rId14" display="mailto:priya.s@email.com"/>
-    <hyperlink ref="I3" r:id="rId15" display="mailto:daniel.c@email.com"/>
-    <hyperlink ref="I13" r:id="rId16" display="mailto:sophia.l@email.com"/>
-    <hyperlink ref="I17" r:id="rId17" display="mailto:james.w@email.com"/>
-    <hyperlink ref="I5" r:id="rId18" display="mailto:olivia.h@email.com"/>
-    <hyperlink ref="I8" r:id="rId19" display="mailto:ethan.a@email.com"/>
-    <hyperlink ref="I19" r:id="rId20" display="mailto:chloe.y@email.com"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:V29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
